--- a/data/nzd0425/nzd0425.xlsx
+++ b/data/nzd0425/nzd0425.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC312"/>
+  <dimension ref="A1:AC313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29269,16 +29269,16 @@
         <v>407.86</v>
       </c>
       <c r="R312" t="n">
-        <v>415.61</v>
+        <v>407.03</v>
       </c>
       <c r="S312" t="n">
-        <v>388.81</v>
+        <v>375.21</v>
       </c>
       <c r="T312" t="n">
         <v>319.74</v>
       </c>
       <c r="U312" t="n">
-        <v>411.92</v>
+        <v>400.18</v>
       </c>
       <c r="V312" t="n">
         <v>385.75</v>
@@ -29302,6 +29302,99 @@
         <v>295.74</v>
       </c>
       <c r="AC312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="C313" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="D313" t="n">
+        <v>374.98</v>
+      </c>
+      <c r="E313" t="n">
+        <v>386.35</v>
+      </c>
+      <c r="F313" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="G313" t="n">
+        <v>381.41</v>
+      </c>
+      <c r="H313" t="n">
+        <v>383.04</v>
+      </c>
+      <c r="I313" t="n">
+        <v>382.86</v>
+      </c>
+      <c r="J313" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="K313" t="n">
+        <v>393.18</v>
+      </c>
+      <c r="L313" t="n">
+        <v>397.34</v>
+      </c>
+      <c r="M313" t="n">
+        <v>402.33</v>
+      </c>
+      <c r="N313" t="n">
+        <v>404.78</v>
+      </c>
+      <c r="O313" t="n">
+        <v>412.35</v>
+      </c>
+      <c r="P313" t="n">
+        <v>415.2</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>404.59</v>
+      </c>
+      <c r="R313" t="n">
+        <v>394.77</v>
+      </c>
+      <c r="S313" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="T313" t="n">
+        <v>293.24</v>
+      </c>
+      <c r="U313" t="n">
+        <v>396.22</v>
+      </c>
+      <c r="V313" t="n">
+        <v>384.66</v>
+      </c>
+      <c r="W313" t="n">
+        <v>370.97</v>
+      </c>
+      <c r="X313" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>331.17</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>310.93</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>296.22</v>
+      </c>
+      <c r="AC313" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29318,7 +29411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B316"/>
+  <dimension ref="A1:B317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32481,6 +32574,16 @@
       </c>
       <c r="B316" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -32649,28 +32752,28 @@
         <v>0.1361</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7606312002350486</v>
+        <v>-0.7560216287945629</v>
       </c>
       <c r="J2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2031289245550039</v>
+        <v>0.2020613006079234</v>
       </c>
       <c r="M2" t="n">
-        <v>8.548254019283167</v>
+        <v>8.544597885833394</v>
       </c>
       <c r="N2" t="n">
-        <v>123.1797994227046</v>
+        <v>122.9519744166017</v>
       </c>
       <c r="O2" t="n">
-        <v>11.09863953026247</v>
+        <v>11.08837113450852</v>
       </c>
       <c r="P2" t="n">
-        <v>388.2319513351038</v>
+        <v>388.1851395938331</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32727,28 +32830,28 @@
         <v>0.1113</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.773124295210767</v>
+        <v>-0.7720245279210675</v>
       </c>
       <c r="J3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1322396828063124</v>
+        <v>0.1327011918673412</v>
       </c>
       <c r="M3" t="n">
-        <v>11.0257872549576</v>
+        <v>10.99605558325478</v>
       </c>
       <c r="N3" t="n">
-        <v>212.8685766695994</v>
+        <v>212.1958105499591</v>
       </c>
       <c r="O3" t="n">
-        <v>14.5900163354809</v>
+        <v>14.56694238850278</v>
       </c>
       <c r="P3" t="n">
-        <v>385.6118628575122</v>
+        <v>385.6006943524812</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32805,28 +32908,28 @@
         <v>0.1963</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6320915359371323</v>
+        <v>-0.6298151093974123</v>
       </c>
       <c r="J4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08665557125135748</v>
+        <v>0.08661704080509058</v>
       </c>
       <c r="M4" t="n">
-        <v>11.33137415218289</v>
+        <v>11.30250274047613</v>
       </c>
       <c r="N4" t="n">
-        <v>228.5456561965458</v>
+        <v>227.8538625855485</v>
       </c>
       <c r="O4" t="n">
-        <v>15.11772655515854</v>
+        <v>15.09482900153388</v>
       </c>
       <c r="P4" t="n">
-        <v>387.8296313742509</v>
+        <v>387.8065135005885</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32883,28 +32986,28 @@
         <v>0.1229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5376746748315244</v>
+        <v>-0.5361185709865084</v>
       </c>
       <c r="J5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04628045717678997</v>
+        <v>0.04632691114880161</v>
       </c>
       <c r="M5" t="n">
-        <v>14.29428231333651</v>
+        <v>14.25407812406202</v>
       </c>
       <c r="N5" t="n">
-        <v>323.323395360177</v>
+        <v>322.3061318581973</v>
       </c>
       <c r="O5" t="n">
-        <v>17.9811956043022</v>
+        <v>17.95288644920914</v>
       </c>
       <c r="P5" t="n">
-        <v>397.8798139358563</v>
+        <v>397.8640111803239</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32961,28 +33064,28 @@
         <v>0.1248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4765438341242472</v>
+        <v>-0.4724756667346172</v>
       </c>
       <c r="J6" t="n">
+        <v>312</v>
+      </c>
+      <c r="K6" t="n">
         <v>311</v>
       </c>
-      <c r="K6" t="n">
-        <v>310</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03267267606376834</v>
+        <v>0.03233922568985537</v>
       </c>
       <c r="M6" t="n">
-        <v>15.04712979156826</v>
+        <v>15.01383705142374</v>
       </c>
       <c r="N6" t="n">
-        <v>364.5621026540118</v>
+        <v>363.5199263568395</v>
       </c>
       <c r="O6" t="n">
-        <v>19.0935094378695</v>
+        <v>19.0661985292517</v>
       </c>
       <c r="P6" t="n">
-        <v>391.6650580626193</v>
+        <v>391.6236670826376</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33039,28 +33142,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4079042446730977</v>
+        <v>-0.4042890818097891</v>
       </c>
       <c r="J7" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K7" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02481687666675958</v>
+        <v>0.02454756877235542</v>
       </c>
       <c r="M7" t="n">
-        <v>14.93166557073373</v>
+        <v>14.89682812338543</v>
       </c>
       <c r="N7" t="n">
-        <v>354.8382516303806</v>
+        <v>353.8036575731482</v>
       </c>
       <c r="O7" t="n">
-        <v>18.8371508363229</v>
+        <v>18.80966925740982</v>
       </c>
       <c r="P7" t="n">
-        <v>386.3204194783696</v>
+        <v>386.2837062891298</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33117,28 +33220,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.134960906468358</v>
+        <v>-0.132619955045879</v>
       </c>
       <c r="J8" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K8" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002409333830243998</v>
+        <v>0.002342512773935046</v>
       </c>
       <c r="M8" t="n">
-        <v>15.88229217352689</v>
+        <v>15.83922379091882</v>
       </c>
       <c r="N8" t="n">
-        <v>409.3042918183289</v>
+        <v>408.0354849828333</v>
       </c>
       <c r="O8" t="n">
-        <v>20.23127014841947</v>
+        <v>20.19988824184018</v>
       </c>
       <c r="P8" t="n">
-        <v>382.8646164754677</v>
+        <v>382.8408433300177</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33195,28 +33298,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08144864611642513</v>
+        <v>0.08040258519865157</v>
       </c>
       <c r="J9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008145936899672801</v>
+        <v>0.0007993030139084034</v>
       </c>
       <c r="M9" t="n">
-        <v>16.01259564757712</v>
+        <v>15.96814506097737</v>
       </c>
       <c r="N9" t="n">
-        <v>441.6189563162707</v>
+        <v>440.2121102340304</v>
       </c>
       <c r="O9" t="n">
-        <v>21.01473188780363</v>
+        <v>20.9812323335411</v>
       </c>
       <c r="P9" t="n">
-        <v>382.3915913820652</v>
+        <v>382.4022144809082</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33273,28 +33376,28 @@
         <v>0.1309</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3523085132867412</v>
+        <v>0.3516190854918209</v>
       </c>
       <c r="J10" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K10" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0144908849740063</v>
+        <v>0.01453353055646944</v>
       </c>
       <c r="M10" t="n">
-        <v>16.72925371160662</v>
+        <v>16.67972069789697</v>
       </c>
       <c r="N10" t="n">
-        <v>458.1281086316472</v>
+        <v>456.6634846156443</v>
       </c>
       <c r="O10" t="n">
-        <v>21.40392741138054</v>
+        <v>21.36968611411137</v>
       </c>
       <c r="P10" t="n">
-        <v>383.8934803385288</v>
+        <v>383.9004817086078</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33351,28 +33454,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6481682155950835</v>
+        <v>0.6474349839736522</v>
       </c>
       <c r="J11" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K11" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04853240279847404</v>
+        <v>0.04874685510068988</v>
       </c>
       <c r="M11" t="n">
-        <v>16.88121672818836</v>
+        <v>16.83145981953103</v>
       </c>
       <c r="N11" t="n">
-        <v>447.0052229835484</v>
+        <v>445.5767389776457</v>
       </c>
       <c r="O11" t="n">
-        <v>21.14249803082759</v>
+        <v>21.10868870815157</v>
       </c>
       <c r="P11" t="n">
-        <v>377.4864714194119</v>
+        <v>377.4939176320147</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33429,28 +33532,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8412786971716156</v>
+        <v>0.8428315235989268</v>
       </c>
       <c r="J12" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K12" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06950380805988043</v>
+        <v>0.07018979458785313</v>
       </c>
       <c r="M12" t="n">
-        <v>18.23712684606434</v>
+        <v>18.18501195428466</v>
       </c>
       <c r="N12" t="n">
-        <v>514.2339090998399</v>
+        <v>512.6046728516316</v>
       </c>
       <c r="O12" t="n">
-        <v>22.67672615480109</v>
+        <v>22.64077456386224</v>
       </c>
       <c r="P12" t="n">
-        <v>373.0280719382354</v>
+        <v>373.012302465977</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33507,28 +33610,28 @@
         <v>0.1835</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7214379539663168</v>
+        <v>0.724010202749462</v>
       </c>
       <c r="J13" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K13" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04783583493435406</v>
+        <v>0.0484744669725955</v>
       </c>
       <c r="M13" t="n">
-        <v>18.84368288650451</v>
+        <v>18.79479690280952</v>
       </c>
       <c r="N13" t="n">
-        <v>562.2524722671383</v>
+        <v>560.5023775697771</v>
       </c>
       <c r="O13" t="n">
-        <v>23.71186353425513</v>
+        <v>23.67493141636903</v>
       </c>
       <c r="P13" t="n">
-        <v>379.5274033564621</v>
+        <v>379.5012813088758</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33585,28 +33688,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.691610920610096</v>
+        <v>0.694281736565348</v>
       </c>
       <c r="J14" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K14" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0479028708977205</v>
+        <v>0.04856887724828363</v>
       </c>
       <c r="M14" t="n">
-        <v>18.77230017133884</v>
+        <v>18.72296206126732</v>
       </c>
       <c r="N14" t="n">
-        <v>515.962721684253</v>
+        <v>514.3650528825355</v>
       </c>
       <c r="O14" t="n">
-        <v>22.71481282520842</v>
+        <v>22.67961756473278</v>
       </c>
       <c r="P14" t="n">
-        <v>382.5957406723293</v>
+        <v>382.5686176421099</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33663,28 +33766,28 @@
         <v>0.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>0.177037635579223</v>
+        <v>0.1877799127412862</v>
       </c>
       <c r="J15" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K15" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002164445967656192</v>
+        <v>0.002448801512844989</v>
       </c>
       <c r="M15" t="n">
-        <v>23.17186833665318</v>
+        <v>23.13379286402014</v>
       </c>
       <c r="N15" t="n">
-        <v>785.8723352958517</v>
+        <v>784.2207582786357</v>
       </c>
       <c r="O15" t="n">
-        <v>28.03341462069599</v>
+        <v>28.00394183465313</v>
       </c>
       <c r="P15" t="n">
-        <v>391.0664593789297</v>
+        <v>390.9578488873935</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33741,28 +33844,28 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1241527602149984</v>
+        <v>0.143207156612826</v>
       </c>
       <c r="J16" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K16" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003913845972804975</v>
+        <v>0.0005236270966293421</v>
       </c>
       <c r="M16" t="n">
-        <v>31.79278889914568</v>
+        <v>31.7306323256958</v>
       </c>
       <c r="N16" t="n">
-        <v>2078.595833666933</v>
+        <v>2074.613626216266</v>
       </c>
       <c r="O16" t="n">
-        <v>45.59162021322485</v>
+        <v>45.54792669503482</v>
       </c>
       <c r="P16" t="n">
-        <v>382.7008413507771</v>
+        <v>382.5033074391691</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33819,28 +33922,28 @@
         <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3725084486741853</v>
+        <v>0.3960921985633516</v>
       </c>
       <c r="J17" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K17" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00398410588725695</v>
+        <v>0.0045258581407841</v>
       </c>
       <c r="M17" t="n">
-        <v>30.83495549837389</v>
+        <v>30.81198411975199</v>
       </c>
       <c r="N17" t="n">
-        <v>1812.581899175912</v>
+        <v>1810.45385326339</v>
       </c>
       <c r="O17" t="n">
-        <v>42.57442776099183</v>
+        <v>42.54942835413174</v>
       </c>
       <c r="P17" t="n">
-        <v>360.454187044526</v>
+        <v>360.209981775482</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -33901,28 +34004,28 @@
         <v>0.0464</v>
       </c>
       <c r="I18" t="n">
-        <v>2.398558146859196</v>
+        <v>2.394951023506169</v>
       </c>
       <c r="J18" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K18" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2476261149610006</v>
+        <v>0.2485972284986817</v>
       </c>
       <c r="M18" t="n">
-        <v>23.74408033529857</v>
+        <v>23.64472115674442</v>
       </c>
       <c r="N18" t="n">
-        <v>969.3361230971517</v>
+        <v>964.8745213231696</v>
       </c>
       <c r="O18" t="n">
-        <v>31.13416327922033</v>
+        <v>31.06242941759658</v>
       </c>
       <c r="P18" t="n">
-        <v>329.4682678359815</v>
+        <v>329.5042921600315</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -33983,28 +34086,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>1.141728052716208</v>
+        <v>1.114922671943522</v>
       </c>
       <c r="J19" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K19" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03832186094722967</v>
+        <v>0.03682315669856762</v>
       </c>
       <c r="M19" t="n">
-        <v>30.14637528430022</v>
+        <v>30.13739304252579</v>
       </c>
       <c r="N19" t="n">
-        <v>1797.399914921298</v>
+        <v>1793.260821299827</v>
       </c>
       <c r="O19" t="n">
-        <v>42.39575350104415</v>
+        <v>42.34691041032187</v>
       </c>
       <c r="P19" t="n">
-        <v>345.0653313443543</v>
+        <v>345.3349774131781</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -34065,28 +34168,28 @@
         <v>0.0269</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2795913539322391</v>
+        <v>-0.3212519610718385</v>
       </c>
       <c r="J20" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K20" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003110714852932461</v>
+        <v>0.004092774558747125</v>
       </c>
       <c r="M20" t="n">
-        <v>24.91672412829195</v>
+        <v>25.08756287900696</v>
       </c>
       <c r="N20" t="n">
-        <v>1410.707739153158</v>
+        <v>1419.389597763015</v>
       </c>
       <c r="O20" t="n">
-        <v>37.55938949388232</v>
+        <v>37.67478729552451</v>
       </c>
       <c r="P20" t="n">
-        <v>363.3159760700033</v>
+        <v>363.7319787040783</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -34147,28 +34250,28 @@
         <v>0.0312</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.094565693657347</v>
+        <v>-1.060797935350771</v>
       </c>
       <c r="J21" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K21" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03477645768322024</v>
+        <v>0.03282007149121058</v>
       </c>
       <c r="M21" t="n">
-        <v>29.90907385905724</v>
+        <v>29.95075605575913</v>
       </c>
       <c r="N21" t="n">
-        <v>1831.168713571186</v>
+        <v>1832.837028348884</v>
       </c>
       <c r="O21" t="n">
-        <v>42.79215715024409</v>
+        <v>42.81164594300112</v>
       </c>
       <c r="P21" t="n">
-        <v>360.7071204525079</v>
+        <v>360.3652439015865</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -34229,28 +34332,28 @@
         <v>0.0247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.663601421443423</v>
+        <v>0.672676713305955</v>
       </c>
       <c r="J22" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K22" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03512828811276159</v>
+        <v>0.03627354363585256</v>
       </c>
       <c r="M22" t="n">
-        <v>19.39887680655577</v>
+        <v>19.37423169235562</v>
       </c>
       <c r="N22" t="n">
-        <v>659.478479585933</v>
+        <v>657.9516147159569</v>
       </c>
       <c r="O22" t="n">
-        <v>25.6803130741417</v>
+        <v>25.65056753204414</v>
       </c>
       <c r="P22" t="n">
-        <v>353.4143638761955</v>
+        <v>353.3225466192259</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -34311,28 +34414,28 @@
         <v>0.0528</v>
       </c>
       <c r="I23" t="n">
-        <v>1.216270251255557</v>
+        <v>1.217970571682855</v>
       </c>
       <c r="J23" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K23" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1688888170486312</v>
+        <v>0.170245439658976</v>
       </c>
       <c r="M23" t="n">
-        <v>15.2493823621526</v>
+        <v>15.20725138803421</v>
       </c>
       <c r="N23" t="n">
-        <v>396.3412864993671</v>
+        <v>395.0855899425735</v>
       </c>
       <c r="O23" t="n">
-        <v>19.90832204128131</v>
+        <v>19.87676004641032</v>
       </c>
       <c r="P23" t="n">
-        <v>336.6711792503736</v>
+        <v>336.6539159441283</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34389,28 +34492,28 @@
         <v>0.0794</v>
       </c>
       <c r="I24" t="n">
-        <v>1.163879410196008</v>
+        <v>1.163975336504235</v>
       </c>
       <c r="J24" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K24" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L24" t="n">
-        <v>0.135920069964794</v>
+        <v>0.1367514303083855</v>
       </c>
       <c r="M24" t="n">
-        <v>16.94999470593986</v>
+        <v>16.89584219108908</v>
       </c>
       <c r="N24" t="n">
-        <v>466.5398916255091</v>
+        <v>465.034996540915</v>
       </c>
       <c r="O24" t="n">
-        <v>21.59953452335279</v>
+        <v>21.56467010044241</v>
       </c>
       <c r="P24" t="n">
-        <v>335.5662508529441</v>
+        <v>335.5652730756814</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34467,28 +34570,28 @@
         <v>0.1141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.098553413127917</v>
+        <v>1.10274500622264</v>
       </c>
       <c r="J25" t="n">
+        <v>312</v>
+      </c>
+      <c r="K25" t="n">
         <v>311</v>
       </c>
-      <c r="K25" t="n">
-        <v>310</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1308620369364096</v>
+        <v>0.1324850450558031</v>
       </c>
       <c r="M25" t="n">
-        <v>16.15979996738456</v>
+        <v>16.13205905790571</v>
       </c>
       <c r="N25" t="n">
-        <v>435.9258536179133</v>
+        <v>434.6627292515238</v>
       </c>
       <c r="O25" t="n">
-        <v>20.87883745848684</v>
+        <v>20.84856659944572</v>
       </c>
       <c r="P25" t="n">
-        <v>319.943204663032</v>
+        <v>319.9006509818216</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34545,28 +34648,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9271355827165405</v>
+        <v>0.9309962890475809</v>
       </c>
       <c r="J26" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K26" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1107275113446696</v>
+        <v>0.1122037008900983</v>
       </c>
       <c r="M26" t="n">
-        <v>15.37749386751958</v>
+        <v>15.347174272108</v>
       </c>
       <c r="N26" t="n">
-        <v>374.6629457569186</v>
+        <v>373.5792367749449</v>
       </c>
       <c r="O26" t="n">
-        <v>19.35621207150094</v>
+        <v>19.32819797019228</v>
       </c>
       <c r="P26" t="n">
-        <v>300.9877759616524</v>
+        <v>300.9485691962894</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34623,28 +34726,28 @@
         <v>0.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8648898660098395</v>
+        <v>0.8652098846314471</v>
       </c>
       <c r="J27" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K27" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1139029055484457</v>
+        <v>0.1146767876777206</v>
       </c>
       <c r="M27" t="n">
-        <v>14.11873905503612</v>
+        <v>14.07508104405046</v>
       </c>
       <c r="N27" t="n">
-        <v>315.8224904679383</v>
+        <v>314.8110437166875</v>
       </c>
       <c r="O27" t="n">
-        <v>17.77139528759457</v>
+        <v>17.74291531053134</v>
       </c>
       <c r="P27" t="n">
-        <v>287.9437364380352</v>
+        <v>287.94048654179</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34701,28 +34804,28 @@
         <v>0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9023072526107659</v>
+        <v>0.8988396007782821</v>
       </c>
       <c r="J28" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K28" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1420229466773169</v>
+        <v>0.1418830664006736</v>
       </c>
       <c r="M28" t="n">
-        <v>13.1071499936709</v>
+        <v>13.08180606494186</v>
       </c>
       <c r="N28" t="n">
-        <v>266.9322069338761</v>
+        <v>266.171152341377</v>
       </c>
       <c r="O28" t="n">
-        <v>16.33806007253848</v>
+        <v>16.31475259822768</v>
       </c>
       <c r="P28" t="n">
-        <v>278.2171981259025</v>
+        <v>278.2524132912374</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34760,7 +34863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC312"/>
+  <dimension ref="A1:AC313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80180,12 +80283,12 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>-43.21926145548858,170.16072010046315</t>
+          <t>-43.2193227568855,170.1607842861732</t>
         </is>
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>-43.219053178980275,170.16165423021127</t>
+          <t>-43.21915277505143,170.16175148031053</t>
         </is>
       </c>
       <c r="T312" t="inlineStr">
@@ -80195,7 +80298,7 @@
       </c>
       <c r="U312" t="inlineStr">
         <is>
-          <t>-43.21809951694943,170.16292744425368</t>
+          <t>-43.21818549123694,170.16301139388676</t>
         </is>
       </c>
       <c r="V312" t="inlineStr">
@@ -80234,6 +80337,153 @@
         </is>
       </c>
       <c r="AC312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-43.22601423441273,170.1501387822603</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-43.225858155663495,170.15101489091757</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-43.22556423765871,170.1518257198331</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-43.225259130552104,170.1525556784375</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-43.22490525923532,170.153205804883</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-43.22452715450532,170.153927267782</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-43.22410289107911,170.15461227235818</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-43.223691494122995,170.15531092937766</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-43.22322776750493,170.15591592743758</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-43.22277746170665,170.15650662283852</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-43.222275253885385,170.1570685403303</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-43.22176178060186,170.1576314661494</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-43.22126412594174,170.15821694809696</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-43.220734574306995,170.1587569634219</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>-43.22023442081093,170.15933889369</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>-43.21979626209585,170.16007143238835</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>-43.21941035066576,170.1608760016397</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>-43.21935965635538,170.16195348978854</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>-43.21936084646462,170.1630568687813</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>-43.2182144910691,170.16303971085134</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>-43.21790693165967,170.16384160760606</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>-43.217614967261795,170.16465873623335</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>-43.21727124163494,170.1653918192988</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>-43.21686325879051,170.16604381683467</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>-43.21644787004856,170.16678141332977</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>-43.2160096460488,170.16748628039568</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>-43.215542730320344,170.1681355471873</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0425/nzd0425.xlsx
+++ b/data/nzd0425/nzd0425.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC313"/>
+  <dimension ref="A1:AC314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29275,7 +29275,7 @@
         <v>375.21</v>
       </c>
       <c r="T312" t="n">
-        <v>319.74</v>
+        <v>357.85</v>
       </c>
       <c r="U312" t="n">
         <v>400.18</v>
@@ -29368,7 +29368,7 @@
         <v>346.96</v>
       </c>
       <c r="T313" t="n">
-        <v>293.24</v>
+        <v>374.27</v>
       </c>
       <c r="U313" t="n">
         <v>396.22</v>
@@ -29395,6 +29395,99 @@
         <v>296.22</v>
       </c>
       <c r="AC313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>371.81</v>
+      </c>
+      <c r="C314" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="D314" t="n">
+        <v>371.02</v>
+      </c>
+      <c r="E314" t="n">
+        <v>382.82</v>
+      </c>
+      <c r="F314" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="G314" t="n">
+        <v>379.47</v>
+      </c>
+      <c r="H314" t="n">
+        <v>382.69</v>
+      </c>
+      <c r="I314" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="J314" t="n">
+        <v>395.25</v>
+      </c>
+      <c r="K314" t="n">
+        <v>396.4</v>
+      </c>
+      <c r="L314" t="n">
+        <v>400.82</v>
+      </c>
+      <c r="M314" t="n">
+        <v>405.43</v>
+      </c>
+      <c r="N314" t="n">
+        <v>408.21</v>
+      </c>
+      <c r="O314" t="n">
+        <v>416.53</v>
+      </c>
+      <c r="P314" t="n">
+        <v>415.78</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>404.59</v>
+      </c>
+      <c r="R314" t="n">
+        <v>394.77</v>
+      </c>
+      <c r="S314" t="n">
+        <v>335.37</v>
+      </c>
+      <c r="T314" t="n">
+        <v>375.48</v>
+      </c>
+      <c r="U314" t="n">
+        <v>390.61</v>
+      </c>
+      <c r="V314" t="n">
+        <v>379.97</v>
+      </c>
+      <c r="W314" t="n">
+        <v>368.63</v>
+      </c>
+      <c r="X314" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>353.76</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>330.07</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>311.41</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>296.94</v>
+      </c>
+      <c r="AC314" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29411,7 +29504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B317"/>
+  <dimension ref="A1:B318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32584,6 +32677,16 @@
       </c>
       <c r="B317" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -32752,28 +32855,28 @@
         <v>0.1361</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7560216287945629</v>
+        <v>-0.7538981036890157</v>
       </c>
       <c r="J2" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K2" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2020613006079234</v>
+        <v>0.2022245754736929</v>
       </c>
       <c r="M2" t="n">
-        <v>8.544597885833394</v>
+        <v>8.528247007204749</v>
       </c>
       <c r="N2" t="n">
-        <v>122.9519744166017</v>
+        <v>122.5946255141602</v>
       </c>
       <c r="O2" t="n">
-        <v>11.08837113450852</v>
+        <v>11.07224573039093</v>
       </c>
       <c r="P2" t="n">
-        <v>388.1851395938331</v>
+        <v>388.1634882837791</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32830,28 +32933,28 @@
         <v>0.1113</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7720245279210675</v>
+        <v>-0.7737502332590123</v>
       </c>
       <c r="J3" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K3" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1327011918673412</v>
+        <v>0.1340050590760627</v>
       </c>
       <c r="M3" t="n">
-        <v>10.99605558325478</v>
+        <v>10.9694455001051</v>
       </c>
       <c r="N3" t="n">
-        <v>212.1958105499591</v>
+        <v>211.5412929455116</v>
       </c>
       <c r="O3" t="n">
-        <v>14.56694238850278</v>
+        <v>14.54445918367237</v>
       </c>
       <c r="P3" t="n">
-        <v>385.6006943524812</v>
+        <v>385.6182895206458</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32908,28 +33011,28 @@
         <v>0.1963</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6298151093974123</v>
+        <v>-0.6300430731988154</v>
       </c>
       <c r="J4" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K4" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08661704080509058</v>
+        <v>0.0872241229697337</v>
       </c>
       <c r="M4" t="n">
-        <v>11.30250274047613</v>
+        <v>11.26790087207235</v>
       </c>
       <c r="N4" t="n">
-        <v>227.8538625855485</v>
+        <v>227.1263037300644</v>
       </c>
       <c r="O4" t="n">
-        <v>15.09482900153388</v>
+        <v>15.07071012693378</v>
       </c>
       <c r="P4" t="n">
-        <v>387.8065135005885</v>
+        <v>387.8088378031985</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32986,28 +33089,28 @@
         <v>0.1229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5361185709865084</v>
+        <v>-0.5367891020058636</v>
       </c>
       <c r="J5" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K5" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04632691114880161</v>
+        <v>0.04674470360149674</v>
       </c>
       <c r="M5" t="n">
-        <v>14.25407812406202</v>
+        <v>14.21284154798231</v>
       </c>
       <c r="N5" t="n">
-        <v>322.3061318581973</v>
+        <v>321.2799362838592</v>
       </c>
       <c r="O5" t="n">
-        <v>17.95288644920914</v>
+        <v>17.92428342455729</v>
       </c>
       <c r="P5" t="n">
-        <v>397.8640111803239</v>
+        <v>397.8708478666259</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33064,28 +33167,28 @@
         <v>0.1248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4724756667346172</v>
+        <v>-0.4708288837172804</v>
       </c>
       <c r="J6" t="n">
+        <v>313</v>
+      </c>
+      <c r="K6" t="n">
         <v>312</v>
       </c>
-      <c r="K6" t="n">
-        <v>311</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03233922568985537</v>
+        <v>0.0323354617450875</v>
       </c>
       <c r="M6" t="n">
-        <v>15.01383705142374</v>
+        <v>14.97174233134978</v>
       </c>
       <c r="N6" t="n">
-        <v>363.5199263568395</v>
+        <v>362.3761263285043</v>
       </c>
       <c r="O6" t="n">
-        <v>19.0661985292517</v>
+        <v>19.03617940471523</v>
       </c>
       <c r="P6" t="n">
-        <v>391.6236670826376</v>
+        <v>391.6068450079199</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33142,28 +33245,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4042890818097891</v>
+        <v>-0.4019229598267781</v>
       </c>
       <c r="J7" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K7" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02454756877235542</v>
+        <v>0.02442962743941868</v>
       </c>
       <c r="M7" t="n">
-        <v>14.89682812338543</v>
+        <v>14.85764560915838</v>
       </c>
       <c r="N7" t="n">
-        <v>353.8036575731482</v>
+        <v>352.7173303897033</v>
       </c>
       <c r="O7" t="n">
-        <v>18.80966925740982</v>
+        <v>18.78077022887249</v>
       </c>
       <c r="P7" t="n">
-        <v>386.2837062891298</v>
+        <v>386.2595814786692</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33220,28 +33323,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.132619955045879</v>
+        <v>-0.1305190603305282</v>
       </c>
       <c r="J8" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K8" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002342512773935046</v>
+        <v>0.002284592287280396</v>
       </c>
       <c r="M8" t="n">
-        <v>15.83922379091882</v>
+        <v>15.79555982431295</v>
       </c>
       <c r="N8" t="n">
-        <v>408.0354849828333</v>
+        <v>406.7665741870118</v>
       </c>
       <c r="O8" t="n">
-        <v>20.19988824184018</v>
+        <v>20.16845492810522</v>
       </c>
       <c r="P8" t="n">
-        <v>382.8408433300177</v>
+        <v>382.8194227578032</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33298,28 +33401,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08040258519865157</v>
+        <v>0.07985670457971877</v>
       </c>
       <c r="J9" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K9" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007993030139084034</v>
+        <v>0.0007939673842345396</v>
       </c>
       <c r="M9" t="n">
-        <v>15.96814506097737</v>
+        <v>15.9206775638947</v>
       </c>
       <c r="N9" t="n">
-        <v>440.2121102340304</v>
+        <v>438.8080256089728</v>
       </c>
       <c r="O9" t="n">
-        <v>20.9812323335411</v>
+        <v>20.9477451199162</v>
       </c>
       <c r="P9" t="n">
-        <v>382.4022144809082</v>
+        <v>382.4077802406453</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33376,28 +33479,28 @@
         <v>0.1309</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3516190854918209</v>
+        <v>0.3530017109880502</v>
       </c>
       <c r="J10" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K10" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01453353055646944</v>
+        <v>0.01474620466793497</v>
       </c>
       <c r="M10" t="n">
-        <v>16.67972069789697</v>
+        <v>16.63211783140824</v>
       </c>
       <c r="N10" t="n">
-        <v>456.6634846156443</v>
+        <v>455.2195321866738</v>
       </c>
       <c r="O10" t="n">
-        <v>21.36968611411137</v>
+        <v>21.33587430096723</v>
       </c>
       <c r="P10" t="n">
-        <v>383.9004817086078</v>
+        <v>383.8863845579647</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33454,28 +33557,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6474349839736522</v>
+        <v>0.6487149934101454</v>
       </c>
       <c r="J11" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K11" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04874685510068988</v>
+        <v>0.04925237317385123</v>
       </c>
       <c r="M11" t="n">
-        <v>16.83145981953103</v>
+        <v>16.78294759353954</v>
       </c>
       <c r="N11" t="n">
-        <v>445.5767389776457</v>
+        <v>444.166058344708</v>
       </c>
       <c r="O11" t="n">
-        <v>21.10868870815157</v>
+        <v>21.0752475274837</v>
       </c>
       <c r="P11" t="n">
-        <v>377.4939176320147</v>
+        <v>377.4808667473753</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33532,28 +33635,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8428315235989268</v>
+        <v>0.8465207914023263</v>
       </c>
       <c r="J12" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K12" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07018979458785313</v>
+        <v>0.0712050372505183</v>
       </c>
       <c r="M12" t="n">
-        <v>18.18501195428466</v>
+        <v>18.14180093677494</v>
       </c>
       <c r="N12" t="n">
-        <v>512.6046728516316</v>
+        <v>511.0740148234532</v>
       </c>
       <c r="O12" t="n">
-        <v>22.64077456386224</v>
+        <v>22.60694616314758</v>
       </c>
       <c r="P12" t="n">
-        <v>373.012302465977</v>
+        <v>372.9746869553928</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33610,28 +33713,28 @@
         <v>0.1835</v>
       </c>
       <c r="I13" t="n">
-        <v>0.724010202749462</v>
+        <v>0.7284766460428481</v>
       </c>
       <c r="J13" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K13" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0484744669725955</v>
+        <v>0.04935588790409984</v>
       </c>
       <c r="M13" t="n">
-        <v>18.79479690280952</v>
+        <v>18.75451373340875</v>
       </c>
       <c r="N13" t="n">
-        <v>560.5023775697771</v>
+        <v>558.8685473298387</v>
       </c>
       <c r="O13" t="n">
-        <v>23.67493141636903</v>
+        <v>23.64040074385032</v>
       </c>
       <c r="P13" t="n">
-        <v>379.5012813088758</v>
+        <v>379.4557417725968</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33688,28 +33791,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.694281736565348</v>
+        <v>0.6990545596100995</v>
       </c>
       <c r="J14" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K14" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04856887724828363</v>
+        <v>0.04951462978874432</v>
       </c>
       <c r="M14" t="n">
-        <v>18.72296206126732</v>
+        <v>18.68226303384916</v>
       </c>
       <c r="N14" t="n">
-        <v>514.3650528825355</v>
+        <v>512.9008916385443</v>
       </c>
       <c r="O14" t="n">
-        <v>22.67961756473278</v>
+        <v>22.64731532960462</v>
       </c>
       <c r="P14" t="n">
-        <v>382.5686176421099</v>
+        <v>382.5199542798051</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33766,28 +33869,28 @@
         <v>0.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1877799127412862</v>
+        <v>0.2010603808689723</v>
       </c>
       <c r="J15" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K15" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002448801512844989</v>
+        <v>0.002821331119517323</v>
       </c>
       <c r="M15" t="n">
-        <v>23.13379286402014</v>
+        <v>23.1045033811054</v>
       </c>
       <c r="N15" t="n">
-        <v>784.2207582786357</v>
+        <v>783.0556133102405</v>
       </c>
       <c r="O15" t="n">
-        <v>28.00394183465313</v>
+        <v>27.98313087040549</v>
       </c>
       <c r="P15" t="n">
-        <v>390.9578488873935</v>
+        <v>390.8230417072804</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33844,28 +33947,28 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.143207156612826</v>
+        <v>0.162395452768983</v>
       </c>
       <c r="J16" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K16" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0005236270966293421</v>
+        <v>0.0006770675009966087</v>
       </c>
       <c r="M16" t="n">
-        <v>31.7306323256958</v>
+        <v>31.66863434266392</v>
       </c>
       <c r="N16" t="n">
-        <v>2074.613626216266</v>
+        <v>2070.707081392524</v>
       </c>
       <c r="O16" t="n">
-        <v>45.54792669503482</v>
+        <v>45.50502259523144</v>
       </c>
       <c r="P16" t="n">
-        <v>382.5033074391691</v>
+        <v>382.3036077987587</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33922,28 +34025,28 @@
         <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3960921985633516</v>
+        <v>0.4193374186695574</v>
       </c>
       <c r="J17" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K17" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0045258581407841</v>
+        <v>0.005096864184115479</v>
       </c>
       <c r="M17" t="n">
-        <v>30.81198411975199</v>
+        <v>30.78732592771294</v>
       </c>
       <c r="N17" t="n">
-        <v>1810.45385326339</v>
+        <v>1808.249057071765</v>
       </c>
       <c r="O17" t="n">
-        <v>42.54942835413174</v>
+        <v>42.52351181489794</v>
       </c>
       <c r="P17" t="n">
-        <v>360.209981775482</v>
+        <v>359.9683689651469</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34004,28 +34107,28 @@
         <v>0.0464</v>
       </c>
       <c r="I18" t="n">
-        <v>2.394951023506169</v>
+        <v>2.396773543171664</v>
       </c>
       <c r="J18" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K18" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2485972284986817</v>
+        <v>0.2501967222331047</v>
       </c>
       <c r="M18" t="n">
-        <v>23.64472115674442</v>
+        <v>23.57282684052182</v>
       </c>
       <c r="N18" t="n">
-        <v>964.8745213231696</v>
+        <v>961.6076572927672</v>
       </c>
       <c r="O18" t="n">
-        <v>31.06242941759658</v>
+        <v>31.00979937524213</v>
       </c>
       <c r="P18" t="n">
-        <v>329.5042921600315</v>
+        <v>329.4857687714021</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -34086,28 +34189,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>1.114922671943522</v>
+        <v>1.089557678289826</v>
       </c>
       <c r="J19" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K19" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03682315669856762</v>
+        <v>0.03537194669633992</v>
       </c>
       <c r="M19" t="n">
-        <v>30.13739304252579</v>
+        <v>30.20816394533677</v>
       </c>
       <c r="N19" t="n">
-        <v>1793.260821299827</v>
+        <v>1792.318792917906</v>
       </c>
       <c r="O19" t="n">
-        <v>42.34691041032187</v>
+        <v>42.33578619699777</v>
       </c>
       <c r="P19" t="n">
-        <v>345.3349774131781</v>
+        <v>345.5918675515992</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -34168,28 +34271,28 @@
         <v>0.0269</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3212519610718385</v>
+        <v>-0.2301591999823465</v>
       </c>
       <c r="J20" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K20" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004092774558747125</v>
+        <v>0.002144175871721887</v>
       </c>
       <c r="M20" t="n">
-        <v>25.08756287900696</v>
+        <v>24.7023852869007</v>
       </c>
       <c r="N20" t="n">
-        <v>1419.389597763015</v>
+        <v>1398.591474854307</v>
       </c>
       <c r="O20" t="n">
-        <v>37.67478729552451</v>
+        <v>37.39774692216507</v>
       </c>
       <c r="P20" t="n">
-        <v>363.7319787040783</v>
+        <v>362.8240036059273</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -34250,28 +34353,28 @@
         <v>0.0312</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.060797935350771</v>
+        <v>-1.023567789248545</v>
       </c>
       <c r="J21" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K21" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03282007149121058</v>
+        <v>0.03065616989899977</v>
       </c>
       <c r="M21" t="n">
-        <v>29.95075605575913</v>
+        <v>30.00595650393079</v>
       </c>
       <c r="N21" t="n">
-        <v>1832.837028348884</v>
+        <v>1837.745185531828</v>
       </c>
       <c r="O21" t="n">
-        <v>42.81164594300112</v>
+        <v>42.86893030543015</v>
       </c>
       <c r="P21" t="n">
-        <v>360.3652439015865</v>
+        <v>359.9874650314364</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -34332,28 +34435,28 @@
         <v>0.0247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.672676713305955</v>
+        <v>0.6785671396445906</v>
       </c>
       <c r="J22" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K22" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03627354363585256</v>
+        <v>0.03712606184881473</v>
       </c>
       <c r="M22" t="n">
-        <v>19.37423169235562</v>
+        <v>19.33616937520302</v>
       </c>
       <c r="N22" t="n">
-        <v>657.9516147159569</v>
+        <v>656.0694648711142</v>
       </c>
       <c r="O22" t="n">
-        <v>25.65056753204414</v>
+        <v>25.61385298761423</v>
       </c>
       <c r="P22" t="n">
-        <v>353.3225466192259</v>
+        <v>353.2627124871205</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -34414,28 +34517,28 @@
         <v>0.0528</v>
       </c>
       <c r="I23" t="n">
-        <v>1.217970571682855</v>
+        <v>1.218099929948911</v>
       </c>
       <c r="J23" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K23" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L23" t="n">
-        <v>0.170245439658976</v>
+        <v>0.1712549533381854</v>
       </c>
       <c r="M23" t="n">
-        <v>15.20725138803421</v>
+        <v>15.15888403970411</v>
       </c>
       <c r="N23" t="n">
-        <v>395.0855899425735</v>
+        <v>393.8153504860306</v>
       </c>
       <c r="O23" t="n">
-        <v>19.87676004641032</v>
+        <v>19.84478144213311</v>
       </c>
       <c r="P23" t="n">
-        <v>336.6539159441283</v>
+        <v>336.6525972808007</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34492,28 +34595,28 @@
         <v>0.0794</v>
       </c>
       <c r="I24" t="n">
-        <v>1.163975336504235</v>
+        <v>1.163129824008114</v>
       </c>
       <c r="J24" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K24" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1367514303083855</v>
+        <v>0.1373961134188625</v>
       </c>
       <c r="M24" t="n">
-        <v>16.89584219108908</v>
+        <v>16.84539994509434</v>
       </c>
       <c r="N24" t="n">
-        <v>465.034996540915</v>
+        <v>463.5453292516766</v>
       </c>
       <c r="O24" t="n">
-        <v>21.56467010044241</v>
+        <v>21.5301028620784</v>
       </c>
       <c r="P24" t="n">
-        <v>335.5652730756814</v>
+        <v>335.5739259903909</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34570,28 +34673,28 @@
         <v>0.1141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.10274500622264</v>
+        <v>1.10597282391365</v>
       </c>
       <c r="J25" t="n">
+        <v>313</v>
+      </c>
+      <c r="K25" t="n">
         <v>312</v>
       </c>
-      <c r="K25" t="n">
-        <v>311</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1324850450558031</v>
+        <v>0.1339367798100796</v>
       </c>
       <c r="M25" t="n">
-        <v>16.13205905790571</v>
+        <v>16.0988149819984</v>
       </c>
       <c r="N25" t="n">
-        <v>434.6627292515238</v>
+        <v>433.3518205863425</v>
       </c>
       <c r="O25" t="n">
-        <v>20.84856659944572</v>
+        <v>20.81710403937931</v>
       </c>
       <c r="P25" t="n">
-        <v>319.9006509818216</v>
+        <v>319.8677500502225</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34648,28 +34751,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9309962890475809</v>
+        <v>0.9340655142841215</v>
       </c>
       <c r="J26" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K26" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1122037008900983</v>
+        <v>0.1135365113335821</v>
       </c>
       <c r="M26" t="n">
-        <v>15.347174272108</v>
+        <v>15.31305375175869</v>
       </c>
       <c r="N26" t="n">
-        <v>373.5792367749449</v>
+        <v>372.4597881650593</v>
       </c>
       <c r="O26" t="n">
-        <v>19.32819797019228</v>
+        <v>19.29921729410442</v>
       </c>
       <c r="P26" t="n">
-        <v>300.9485691962894</v>
+        <v>300.9172755953576</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34726,28 +34829,28 @@
         <v>0.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8652098846314471</v>
+        <v>0.8657811304872012</v>
       </c>
       <c r="J27" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K27" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1146767876777206</v>
+        <v>0.1155159321806069</v>
       </c>
       <c r="M27" t="n">
-        <v>14.07508104405046</v>
+        <v>14.03292755520824</v>
       </c>
       <c r="N27" t="n">
-        <v>314.8110437166875</v>
+        <v>313.8078243582988</v>
       </c>
       <c r="O27" t="n">
-        <v>17.74291531053134</v>
+        <v>17.71462176729435</v>
       </c>
       <c r="P27" t="n">
-        <v>287.94048654179</v>
+        <v>287.934662159913</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34804,28 +34907,28 @@
         <v>0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8988396007782821</v>
+        <v>0.8958221979744287</v>
       </c>
       <c r="J28" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K28" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1418830664006736</v>
+        <v>0.1418747980019793</v>
       </c>
       <c r="M28" t="n">
-        <v>13.08180606494186</v>
+        <v>13.05434256885889</v>
       </c>
       <c r="N28" t="n">
-        <v>266.171152341377</v>
+        <v>265.3923795461833</v>
       </c>
       <c r="O28" t="n">
-        <v>16.31475259822768</v>
+        <v>16.29086798013486</v>
       </c>
       <c r="P28" t="n">
-        <v>278.2524132912374</v>
+        <v>278.283178514353</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34863,7 +34966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC313"/>
+  <dimension ref="A1:AC314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80293,7 +80396,7 @@
       </c>
       <c r="T312" t="inlineStr">
         <is>
-          <t>-43.21916678216399,170.16286737027522</t>
+          <t>-43.218887695228375,170.16259485205293</t>
         </is>
       </c>
       <c r="U312" t="inlineStr">
@@ -80440,7 +80543,7 @@
       </c>
       <c r="T313" t="inlineStr">
         <is>
-          <t>-43.21936084646462,170.1630568687813</t>
+          <t>-43.21876744819513,170.16247743614227</t>
         </is>
       </c>
       <c r="U313" t="inlineStr">
@@ -80484,6 +80587,153 @@
         </is>
       </c>
       <c r="AC313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-43.226047397324386,170.15015448779937</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-43.225896420481426,170.1510330130365</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>-43.225597910636026,170.15184166752894</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-43.22528736405443,170.15257558618418</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-43.22493254854747,170.15323357322242</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-43.22454094809055,170.1539419007904</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-43.22410537960259,170.15461491233538</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-43.2236859482936,170.1553050459939</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-43.22320543598537,170.15588953544042</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-43.22275698473116,170.15647858853333</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-43.222253576100044,170.1570376368349</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-43.221742470018555,170.15760393727382</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>-43.221242759817386,170.15818648882544</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>-43.22070853639912,170.1587198441188</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>-43.220230807913254,170.1593337431795</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>-43.21979626209585,170.16007143238835</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>-43.21941035066576,170.1608760016397</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>-43.219444532520114,170.1620363676958</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>-43.21875858711222,170.1624687837089</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>-43.21825557415375,170.16307982659654</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>-43.21794127725605,170.16387514482147</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>-43.217632103365375,170.1646754691757</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>-43.21728050094265,170.1654031342904</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>-43.216870768140836,170.16605671702635</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>-43.21645357608988,170.16679247279998</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>-43.21600715616227,170.16748145445587</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>-43.21553899552121,170.16812830829988</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0425/nzd0425.xlsx
+++ b/data/nzd0425/nzd0425.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC314"/>
+  <dimension ref="A1:AC316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29488,6 +29488,192 @@
         <v>296.94</v>
       </c>
       <c r="AC314" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>365.66</v>
+      </c>
+      <c r="C315" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="D315" t="n">
+        <v>364.8</v>
+      </c>
+      <c r="E315" t="n">
+        <v>375.66</v>
+      </c>
+      <c r="F315" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="G315" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="H315" t="n">
+        <v>377.68</v>
+      </c>
+      <c r="I315" t="n">
+        <v>381.18</v>
+      </c>
+      <c r="J315" t="n">
+        <v>398.6</v>
+      </c>
+      <c r="K315" t="n">
+        <v>398.38</v>
+      </c>
+      <c r="L315" t="n">
+        <v>404.72</v>
+      </c>
+      <c r="M315" t="n">
+        <v>409.64</v>
+      </c>
+      <c r="N315" t="n">
+        <v>412.12</v>
+      </c>
+      <c r="O315" t="n">
+        <v>423.6</v>
+      </c>
+      <c r="P315" t="n">
+        <v>421.77</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>410.98</v>
+      </c>
+      <c r="R315" t="n">
+        <v>380.57</v>
+      </c>
+      <c r="S315" t="n">
+        <v>321.91</v>
+      </c>
+      <c r="T315" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="U315" t="n">
+        <v>389.32</v>
+      </c>
+      <c r="V315" t="n">
+        <v>380.72</v>
+      </c>
+      <c r="W315" t="n">
+        <v>369.16</v>
+      </c>
+      <c r="X315" t="n">
+        <v>365.51</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>353.54</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>329.72</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>313.54</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>299.88</v>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>364.49</v>
+      </c>
+      <c r="C316" t="n">
+        <v>354.96</v>
+      </c>
+      <c r="D316" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="E316" t="n">
+        <v>372.63</v>
+      </c>
+      <c r="F316" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="G316" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="H316" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="I316" t="n">
+        <v>384.98</v>
+      </c>
+      <c r="J316" t="n">
+        <v>402.05</v>
+      </c>
+      <c r="K316" t="n">
+        <v>402.75</v>
+      </c>
+      <c r="L316" t="n">
+        <v>407.78</v>
+      </c>
+      <c r="M316" t="n">
+        <v>412.56</v>
+      </c>
+      <c r="N316" t="n">
+        <v>418.1</v>
+      </c>
+      <c r="O316" t="n">
+        <v>427.83</v>
+      </c>
+      <c r="P316" t="n">
+        <v>426.89</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>420.89</v>
+      </c>
+      <c r="R316" t="n">
+        <v>380.57</v>
+      </c>
+      <c r="S316" t="n">
+        <v>321.91</v>
+      </c>
+      <c r="T316" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="U316" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="V316" t="n">
+        <v>380.72</v>
+      </c>
+      <c r="W316" t="n">
+        <v>364.57</v>
+      </c>
+      <c r="X316" t="n">
+        <v>362.36</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>350.84</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>329.49</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>302.05</v>
+      </c>
+      <c r="AC316" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29504,7 +29690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B318"/>
+  <dimension ref="A1:B320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32687,6 +32873,26 @@
       </c>
       <c r="B318" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>-0.68</v>
       </c>
     </row>
   </sheetData>
@@ -32855,28 +33061,28 @@
         <v>0.1361</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7538981036890157</v>
+        <v>-0.7580839830545193</v>
       </c>
       <c r="J2" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K2" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2022245754736929</v>
+        <v>0.2061853821327291</v>
       </c>
       <c r="M2" t="n">
-        <v>8.528247007204749</v>
+        <v>8.494423340052576</v>
       </c>
       <c r="N2" t="n">
-        <v>122.5946255141602</v>
+        <v>121.887350929122</v>
       </c>
       <c r="O2" t="n">
-        <v>11.07224573039093</v>
+        <v>11.04026045567413</v>
       </c>
       <c r="P2" t="n">
-        <v>388.1634882837791</v>
+        <v>388.2064024140727</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32933,28 +33139,28 @@
         <v>0.1113</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7737502332590123</v>
+        <v>-0.7857526859926774</v>
       </c>
       <c r="J3" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K3" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1340050590760627</v>
+        <v>0.1389487844403748</v>
       </c>
       <c r="M3" t="n">
-        <v>10.9694455001051</v>
+        <v>10.95900883549113</v>
       </c>
       <c r="N3" t="n">
-        <v>211.5412929455116</v>
+        <v>210.7699814853612</v>
       </c>
       <c r="O3" t="n">
-        <v>14.54445918367237</v>
+        <v>14.51791932355877</v>
       </c>
       <c r="P3" t="n">
-        <v>385.6182895206458</v>
+        <v>385.7413348251441</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33011,28 +33217,28 @@
         <v>0.1963</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6300430731988154</v>
+        <v>-0.6388015717837382</v>
       </c>
       <c r="J4" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K4" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0872241229697337</v>
+        <v>0.09047418063226231</v>
       </c>
       <c r="M4" t="n">
-        <v>11.26790087207235</v>
+        <v>11.25556036862945</v>
       </c>
       <c r="N4" t="n">
-        <v>227.1263037300644</v>
+        <v>225.9878561084492</v>
       </c>
       <c r="O4" t="n">
-        <v>15.07071012693378</v>
+        <v>15.03289247312204</v>
       </c>
       <c r="P4" t="n">
-        <v>387.8088378031985</v>
+        <v>387.8986263032239</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33089,28 +33295,28 @@
         <v>0.1229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5367891020058636</v>
+        <v>-0.5489275422173174</v>
       </c>
       <c r="J5" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04674470360149674</v>
+        <v>0.04933925286936058</v>
       </c>
       <c r="M5" t="n">
-        <v>14.21284154798231</v>
+        <v>14.19971893719083</v>
       </c>
       <c r="N5" t="n">
-        <v>321.2799362838592</v>
+        <v>319.8348719837492</v>
       </c>
       <c r="O5" t="n">
-        <v>17.92428342455729</v>
+        <v>17.88392775605373</v>
       </c>
       <c r="P5" t="n">
-        <v>397.8708478666259</v>
+        <v>397.9952915972567</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33167,28 +33373,28 @@
         <v>0.1248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4708288837172804</v>
+        <v>-0.479721814616701</v>
       </c>
       <c r="J6" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K6" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0323354617450875</v>
+        <v>0.03394992396965446</v>
       </c>
       <c r="M6" t="n">
-        <v>14.97174233134978</v>
+        <v>14.93268676507166</v>
       </c>
       <c r="N6" t="n">
-        <v>362.3761263285043</v>
+        <v>360.3937154189574</v>
       </c>
       <c r="O6" t="n">
-        <v>19.03617940471523</v>
+        <v>18.98403843809207</v>
       </c>
       <c r="P6" t="n">
-        <v>391.6068450079199</v>
+        <v>391.6981908034544</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33245,28 +33451,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4019229598267781</v>
+        <v>-0.4058667316473417</v>
       </c>
       <c r="J7" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K7" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02442962743941868</v>
+        <v>0.02523441020840256</v>
       </c>
       <c r="M7" t="n">
-        <v>14.85764560915838</v>
+        <v>14.78862518222083</v>
       </c>
       <c r="N7" t="n">
-        <v>352.7173303897033</v>
+        <v>350.5393007988244</v>
       </c>
       <c r="O7" t="n">
-        <v>18.78077022887249</v>
+        <v>18.72269480600547</v>
       </c>
       <c r="P7" t="n">
-        <v>386.2595814786692</v>
+        <v>386.3000090605007</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33323,28 +33529,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1305190603305282</v>
+        <v>-0.1317617244622293</v>
       </c>
       <c r="J8" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K8" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002284592287280396</v>
+        <v>0.00236061752286465</v>
       </c>
       <c r="M8" t="n">
-        <v>15.79555982431295</v>
+        <v>15.70355867592867</v>
       </c>
       <c r="N8" t="n">
-        <v>406.7665741870118</v>
+        <v>404.1934533378523</v>
       </c>
       <c r="O8" t="n">
-        <v>20.16845492810522</v>
+        <v>20.10456299793289</v>
       </c>
       <c r="P8" t="n">
-        <v>382.8194227578032</v>
+        <v>382.8321569247338</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33401,28 +33607,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07985670457971877</v>
+        <v>0.07807045728044561</v>
       </c>
       <c r="J9" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K9" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007939673842345396</v>
+        <v>0.0007694107813950302</v>
       </c>
       <c r="M9" t="n">
-        <v>15.9206775638947</v>
+        <v>15.83422591933192</v>
       </c>
       <c r="N9" t="n">
-        <v>438.8080256089728</v>
+        <v>436.057414818808</v>
       </c>
       <c r="O9" t="n">
-        <v>20.9477451199162</v>
+        <v>20.88198780812804</v>
       </c>
       <c r="P9" t="n">
-        <v>382.4077802406453</v>
+        <v>382.4260793966244</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33479,28 +33685,28 @@
         <v>0.1309</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3530017109880502</v>
+        <v>0.3620367429961585</v>
       </c>
       <c r="J10" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K10" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01474620466793497</v>
+        <v>0.01570052058728699</v>
       </c>
       <c r="M10" t="n">
-        <v>16.63211783140824</v>
+        <v>16.56300921795509</v>
       </c>
       <c r="N10" t="n">
-        <v>455.2195321866738</v>
+        <v>452.6695458600068</v>
       </c>
       <c r="O10" t="n">
-        <v>21.33587430096723</v>
+        <v>21.2760321925872</v>
       </c>
       <c r="P10" t="n">
-        <v>383.8863845579647</v>
+        <v>383.7937532600793</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33557,28 +33763,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6487149934101454</v>
+        <v>0.6563631420169027</v>
       </c>
       <c r="J11" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K11" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04925237317385123</v>
+        <v>0.05100132080591646</v>
       </c>
       <c r="M11" t="n">
-        <v>16.78294759353954</v>
+        <v>16.70729157174841</v>
       </c>
       <c r="N11" t="n">
-        <v>444.166058344708</v>
+        <v>441.6063724553739</v>
       </c>
       <c r="O11" t="n">
-        <v>21.0752475274837</v>
+        <v>21.01443247997371</v>
       </c>
       <c r="P11" t="n">
-        <v>377.4808667473753</v>
+        <v>377.4024498179743</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33635,28 +33841,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8465207914023263</v>
+        <v>0.8604591999357456</v>
       </c>
       <c r="J12" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K12" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0712050372505183</v>
+        <v>0.0742399453514434</v>
       </c>
       <c r="M12" t="n">
-        <v>18.14180093677494</v>
+        <v>18.08321864842343</v>
       </c>
       <c r="N12" t="n">
-        <v>511.0740148234532</v>
+        <v>508.6091105727164</v>
       </c>
       <c r="O12" t="n">
-        <v>22.60694616314758</v>
+        <v>22.55236374690503</v>
       </c>
       <c r="P12" t="n">
-        <v>372.9746869553928</v>
+        <v>372.8317912162776</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33713,28 +33919,28 @@
         <v>0.1835</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7284766460428481</v>
+        <v>0.7442564527191186</v>
       </c>
       <c r="J13" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K13" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04935588790409984</v>
+        <v>0.0519991585328663</v>
       </c>
       <c r="M13" t="n">
-        <v>18.75451373340875</v>
+        <v>18.70471681594309</v>
       </c>
       <c r="N13" t="n">
-        <v>558.8685473298387</v>
+        <v>556.314527084722</v>
       </c>
       <c r="O13" t="n">
-        <v>23.64040074385032</v>
+        <v>23.58632076193152</v>
       </c>
       <c r="P13" t="n">
-        <v>379.4557417725968</v>
+        <v>379.2939698398397</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33791,28 +33997,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6990545596100995</v>
+        <v>0.7169887175807823</v>
       </c>
       <c r="J14" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K14" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04951462978874432</v>
+        <v>0.05251303910602967</v>
       </c>
       <c r="M14" t="n">
-        <v>18.68226303384916</v>
+        <v>18.63413681658405</v>
       </c>
       <c r="N14" t="n">
-        <v>512.9008916385443</v>
+        <v>510.9677718659603</v>
       </c>
       <c r="O14" t="n">
-        <v>22.64731532960462</v>
+        <v>22.60459625531853</v>
       </c>
       <c r="P14" t="n">
-        <v>382.5199542798051</v>
+        <v>382.336087797583</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33869,28 +34075,28 @@
         <v>0.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2010603808689723</v>
+        <v>0.2387565397719975</v>
       </c>
       <c r="J15" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K15" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002821331119517323</v>
+        <v>0.004001822013062983</v>
       </c>
       <c r="M15" t="n">
-        <v>23.1045033811054</v>
+        <v>23.08320917827428</v>
       </c>
       <c r="N15" t="n">
-        <v>783.0556133102405</v>
+        <v>783.5746036517269</v>
       </c>
       <c r="O15" t="n">
-        <v>27.98313087040549</v>
+        <v>27.99240260591661</v>
       </c>
       <c r="P15" t="n">
-        <v>390.8230417072804</v>
+        <v>390.4383159843974</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33947,28 +34153,28 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.162395452768983</v>
+        <v>0.2110149998067224</v>
       </c>
       <c r="J16" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K16" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0006770675009966087</v>
+        <v>0.001153737499736796</v>
       </c>
       <c r="M16" t="n">
-        <v>31.66863434266392</v>
+        <v>31.56768550193995</v>
       </c>
       <c r="N16" t="n">
-        <v>2070.707081392524</v>
+        <v>2066.433780564013</v>
       </c>
       <c r="O16" t="n">
-        <v>45.50502259523144</v>
+        <v>45.45804417882509</v>
       </c>
       <c r="P16" t="n">
-        <v>382.3036077987587</v>
+        <v>381.7949050706461</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34025,28 +34231,28 @@
         <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4193374186695574</v>
+        <v>0.4801199465791256</v>
       </c>
       <c r="J17" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K17" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005096864184115479</v>
+        <v>0.006721258263784446</v>
       </c>
       <c r="M17" t="n">
-        <v>30.78732592771294</v>
+        <v>30.78363054381662</v>
       </c>
       <c r="N17" t="n">
-        <v>1808.249057071765</v>
+        <v>1809.543554180407</v>
       </c>
       <c r="O17" t="n">
-        <v>42.52351181489794</v>
+        <v>42.53873004898485</v>
       </c>
       <c r="P17" t="n">
-        <v>359.9683689651469</v>
+        <v>359.3333022670076</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34107,28 +34313,28 @@
         <v>0.0464</v>
       </c>
       <c r="I18" t="n">
-        <v>2.396773543171664</v>
+        <v>2.38158378064525</v>
       </c>
       <c r="J18" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K18" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2501967222331047</v>
+        <v>0.2502815170123232</v>
       </c>
       <c r="M18" t="n">
-        <v>23.57282684052182</v>
+        <v>23.49658906149294</v>
       </c>
       <c r="N18" t="n">
-        <v>961.6076572927672</v>
+        <v>956.0010740731371</v>
       </c>
       <c r="O18" t="n">
-        <v>31.00979937524213</v>
+        <v>30.91926703647965</v>
       </c>
       <c r="P18" t="n">
-        <v>329.4857687714021</v>
+        <v>329.6410339035341</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -34189,28 +34395,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>1.089557678289826</v>
+        <v>1.022346331266998</v>
       </c>
       <c r="J19" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K19" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03537194669633992</v>
+        <v>0.03140849931203327</v>
       </c>
       <c r="M19" t="n">
-        <v>30.20816394533677</v>
+        <v>30.4541044946537</v>
       </c>
       <c r="N19" t="n">
-        <v>1792.318792917906</v>
+        <v>1798.111561318788</v>
       </c>
       <c r="O19" t="n">
-        <v>42.33578619699777</v>
+        <v>42.4041455676068</v>
       </c>
       <c r="P19" t="n">
-        <v>345.5918675515992</v>
+        <v>346.2763249566978</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -34271,28 +34477,28 @@
         <v>0.0269</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2301591999823465</v>
+        <v>-0.21833285477959</v>
       </c>
       <c r="J20" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K20" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002144175871721887</v>
+        <v>0.001955963054894205</v>
       </c>
       <c r="M20" t="n">
-        <v>24.7023852869007</v>
+        <v>24.59601623490624</v>
       </c>
       <c r="N20" t="n">
-        <v>1398.591474854307</v>
+        <v>1390.30888667765</v>
       </c>
       <c r="O20" t="n">
-        <v>37.39774692216507</v>
+        <v>37.28684602748871</v>
       </c>
       <c r="P20" t="n">
-        <v>362.8240036059273</v>
+        <v>362.704801242308</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -34353,28 +34559,28 @@
         <v>0.0312</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.023567789248545</v>
+        <v>-0.964423266723055</v>
       </c>
       <c r="J21" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K21" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03065616989899977</v>
+        <v>0.02747251799410277</v>
       </c>
       <c r="M21" t="n">
-        <v>30.00595650393079</v>
+        <v>30.05005359955236</v>
       </c>
       <c r="N21" t="n">
-        <v>1837.745185531828</v>
+        <v>1840.172730576932</v>
       </c>
       <c r="O21" t="n">
-        <v>42.86893030543015</v>
+        <v>42.89723453297347</v>
       </c>
       <c r="P21" t="n">
-        <v>359.9874650314364</v>
+        <v>359.3840342845893</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -34435,28 +34641,28 @@
         <v>0.0247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6785671396445906</v>
+        <v>0.690972645675528</v>
       </c>
       <c r="J22" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K22" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03712606184881473</v>
+        <v>0.03893730266138784</v>
       </c>
       <c r="M22" t="n">
-        <v>19.33616937520302</v>
+        <v>19.26353132043547</v>
       </c>
       <c r="N22" t="n">
-        <v>656.0694648711142</v>
+        <v>652.405169715446</v>
       </c>
       <c r="O22" t="n">
-        <v>25.61385298761423</v>
+        <v>25.5422232727585</v>
       </c>
       <c r="P22" t="n">
-        <v>353.2627124871205</v>
+        <v>353.136012899546</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -34517,28 +34723,28 @@
         <v>0.0528</v>
       </c>
       <c r="I23" t="n">
-        <v>1.218099929948911</v>
+        <v>1.215943238727234</v>
       </c>
       <c r="J23" t="n">
+        <v>315</v>
+      </c>
+      <c r="K23" t="n">
         <v>313</v>
       </c>
-      <c r="K23" t="n">
-        <v>311</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1712549533381854</v>
+        <v>0.1727054911357586</v>
       </c>
       <c r="M23" t="n">
-        <v>15.15888403970411</v>
+        <v>15.07882176473464</v>
       </c>
       <c r="N23" t="n">
-        <v>393.8153504860306</v>
+        <v>391.3513372492301</v>
       </c>
       <c r="O23" t="n">
-        <v>19.84478144213311</v>
+        <v>19.78260188269556</v>
       </c>
       <c r="P23" t="n">
-        <v>336.6525972808007</v>
+        <v>336.6747174235467</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34595,28 +34801,28 @@
         <v>0.0794</v>
       </c>
       <c r="I24" t="n">
-        <v>1.163129824008114</v>
+        <v>1.160451357141703</v>
       </c>
       <c r="J24" t="n">
+        <v>315</v>
+      </c>
+      <c r="K24" t="n">
         <v>313</v>
       </c>
-      <c r="K24" t="n">
-        <v>311</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.1373961134188625</v>
+        <v>0.1384846588801651</v>
       </c>
       <c r="M24" t="n">
-        <v>16.84539994509434</v>
+        <v>16.74984088104743</v>
       </c>
       <c r="N24" t="n">
-        <v>463.5453292516766</v>
+        <v>460.6277474514733</v>
       </c>
       <c r="O24" t="n">
-        <v>21.5301028620784</v>
+        <v>21.4622400380639</v>
       </c>
       <c r="P24" t="n">
-        <v>335.5739259903909</v>
+        <v>335.6014968433881</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34673,28 +34879,28 @@
         <v>0.1141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.10597282391365</v>
+        <v>1.110164744599641</v>
       </c>
       <c r="J25" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K25" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1339367798100796</v>
+        <v>0.1364198641160527</v>
       </c>
       <c r="M25" t="n">
-        <v>16.0988149819984</v>
+        <v>16.02012785366533</v>
       </c>
       <c r="N25" t="n">
-        <v>433.3518205863425</v>
+        <v>430.6730436661201</v>
       </c>
       <c r="O25" t="n">
-        <v>20.81710403937931</v>
+        <v>20.75266353184863</v>
       </c>
       <c r="P25" t="n">
-        <v>319.8677500502225</v>
+        <v>319.8247978680794</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34751,28 +34957,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9340655142841215</v>
+        <v>0.9393522937259393</v>
       </c>
       <c r="J26" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K26" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1135365113335821</v>
+        <v>0.1160641285697491</v>
       </c>
       <c r="M26" t="n">
-        <v>15.31305375175869</v>
+        <v>15.24107510282984</v>
       </c>
       <c r="N26" t="n">
-        <v>372.4597881650593</v>
+        <v>370.2052048842988</v>
       </c>
       <c r="O26" t="n">
-        <v>19.29921729410442</v>
+        <v>19.24071736927443</v>
       </c>
       <c r="P26" t="n">
-        <v>300.9172755953576</v>
+        <v>300.8630803220225</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34829,28 +35035,28 @@
         <v>0.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8657811304872012</v>
+        <v>0.8706780774212752</v>
       </c>
       <c r="J27" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K27" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1155159321806069</v>
+        <v>0.1180784396344458</v>
       </c>
       <c r="M27" t="n">
-        <v>14.03292755520824</v>
+        <v>13.96761213834211</v>
       </c>
       <c r="N27" t="n">
-        <v>313.8078243582988</v>
+        <v>311.9157826165528</v>
       </c>
       <c r="O27" t="n">
-        <v>17.71462176729435</v>
+        <v>17.66113763653273</v>
       </c>
       <c r="P27" t="n">
-        <v>287.934662159913</v>
+        <v>287.8844561858941</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34907,28 +35113,28 @@
         <v>0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8958221979744287</v>
+        <v>0.8948240124683876</v>
       </c>
       <c r="J28" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K28" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1418747980019793</v>
+        <v>0.1432943062322382</v>
       </c>
       <c r="M28" t="n">
-        <v>13.05434256885889</v>
+        <v>12.97798368062196</v>
       </c>
       <c r="N28" t="n">
-        <v>265.3923795461833</v>
+        <v>263.7185961637164</v>
       </c>
       <c r="O28" t="n">
-        <v>16.29086798013486</v>
+        <v>16.23941489597813</v>
       </c>
       <c r="P28" t="n">
-        <v>278.283178514353</v>
+        <v>278.2934043150889</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34966,7 +35172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC314"/>
+  <dimension ref="A1:AC316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80739,6 +80945,300 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-43.22609969268132,170.15017925425926</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-43.22594846062984,170.15105765915297</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>-43.2256508010157,170.15186671672132</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-43.2253446308656,170.15261596569138</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-43.22499160317545,170.1532936645806</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-43.224590932047406,170.15399492664358</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-43.224141001032386,170.15465270174658</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-43.22370343898537,170.15532360128475</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-43.22318262787267,170.15586258021926</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-43.22274439329586,170.15646135005687</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-43.22222928202099,170.15700300363335</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-43.22171624499066,170.1575665513126</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>-43.2212184036722,170.158151767058</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>-43.220664496180014,170.1586570610634</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>-43.22019349538848,170.15928055087394</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>-43.219754061032425,170.1600180246192</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>-43.21951180504154,170.1609822303193</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>-43.21954310304483,170.162132617906</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>-43.218749799260785,170.16246020278572</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>-43.218265021064454,170.16308905108025</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>-43.21793578489049,170.16386978172483</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>-43.21762822211134,170.16467167923494</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>-43.21727439516739,170.16539567295496</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>-43.21687200101913,170.16605883496857</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>-43.21645539164826,170.16679599172278</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>-43.215996107288426,170.16746003935282</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>-43.215523745086834,170.16809874951903</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-43.22610964155359,170.1501839659318</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-43.225962576094155,170.1510643442176</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>-43.22565887912795,170.1518705425662</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-43.225368865280466,170.15263305368936</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-43.22501333353861,170.15331577646623</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-43.22458879901984,170.15399266380314</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-43.22413062033746,170.15464168925897</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-43.22367642084244,170.1552949386448</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-43.22315913891467,170.1558348203855</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-43.222716603099244,170.15642330354555</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-43.22221022050592,170.15697582990992</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>-43.221698055653434,170.15754062092608</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>-43.221181153078156,170.15809866323198</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>-43.22063814678315,170.15861949783599</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>-43.2201616021937,170.15923508438053</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>-43.219688613015,170.15993519675342</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>-43.21951180504154,170.1609822303193</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>-43.21954310304483,170.162132617906</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>-43.21890863958468,170.1626153033483</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>-43.218407164034225,170.1632278477212</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>-43.21793578489049,170.16386978172483</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>-43.21766183523209,170.1647045015677</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>-43.217295530541364,170.1654215006608</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>-43.21688713179502,170.16608482790286</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>-43.216456584729436,170.16679830415785</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>-43.215985940246206,170.16744033344327</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>-43.21551248880919,170.1680769323332</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0425/nzd0425.xlsx
+++ b/data/nzd0425/nzd0425.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC316"/>
+  <dimension ref="A1:AC317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29641,7 +29641,7 @@
         <v>420.89</v>
       </c>
       <c r="R316" t="n">
-        <v>380.57</v>
+        <v>389.97</v>
       </c>
       <c r="S316" t="n">
         <v>321.91</v>
@@ -29653,7 +29653,7 @@
         <v>369.91</v>
       </c>
       <c r="V316" t="n">
-        <v>380.72</v>
+        <v>368.82</v>
       </c>
       <c r="W316" t="n">
         <v>364.57</v>
@@ -29674,6 +29674,99 @@
         <v>302.05</v>
       </c>
       <c r="AC316" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>362.78</v>
+      </c>
+      <c r="C317" t="n">
+        <v>350.62</v>
+      </c>
+      <c r="D317" t="n">
+        <v>356.17</v>
+      </c>
+      <c r="E317" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="F317" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="G317" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="H317" t="n">
+        <v>379.84</v>
+      </c>
+      <c r="I317" t="n">
+        <v>389.76</v>
+      </c>
+      <c r="J317" t="n">
+        <v>407.93</v>
+      </c>
+      <c r="K317" t="n">
+        <v>409.79</v>
+      </c>
+      <c r="L317" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="M317" t="n">
+        <v>421.69</v>
+      </c>
+      <c r="N317" t="n">
+        <v>430.01</v>
+      </c>
+      <c r="O317" t="n">
+        <v>439.28</v>
+      </c>
+      <c r="P317" t="n">
+        <v>436.82</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>436.43</v>
+      </c>
+      <c r="R317" t="n">
+        <v>384.14</v>
+      </c>
+      <c r="S317" t="n">
+        <v>304.55</v>
+      </c>
+      <c r="T317" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="U317" t="n">
+        <v>345.18</v>
+      </c>
+      <c r="V317" t="n">
+        <v>350.45</v>
+      </c>
+      <c r="W317" t="n">
+        <v>357.07</v>
+      </c>
+      <c r="X317" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>326.63</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>316.03</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>305.91</v>
+      </c>
+      <c r="AC317" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29690,7 +29783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32893,6 +32986,16 @@
       </c>
       <c r="B320" t="n">
         <v>-0.68</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -33061,28 +33164,28 @@
         <v>0.1361</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7580839830545193</v>
+        <v>-0.7615334912785322</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2061853821327291</v>
+        <v>0.2086791423864535</v>
       </c>
       <c r="M2" t="n">
-        <v>8.494423340052576</v>
+        <v>8.484401624457048</v>
       </c>
       <c r="N2" t="n">
-        <v>121.887350929122</v>
+        <v>121.5970242886782</v>
       </c>
       <c r="O2" t="n">
-        <v>11.04026045567413</v>
+        <v>11.02710407535352</v>
       </c>
       <c r="P2" t="n">
-        <v>388.2064024140727</v>
+        <v>388.2418512674314</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33139,28 +33242,28 @@
         <v>0.1113</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7857526859926774</v>
+        <v>-0.7948086146639979</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1389487844403748</v>
+        <v>0.1421701834525344</v>
       </c>
       <c r="M3" t="n">
-        <v>10.95900883549113</v>
+        <v>10.96904544143041</v>
       </c>
       <c r="N3" t="n">
-        <v>210.7699814853612</v>
+        <v>210.7604448297509</v>
       </c>
       <c r="O3" t="n">
-        <v>14.51791932355877</v>
+        <v>14.5175908755465</v>
       </c>
       <c r="P3" t="n">
-        <v>385.7413348251441</v>
+        <v>385.8343980291282</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33217,28 +33320,28 @@
         <v>0.1963</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6388015717837382</v>
+        <v>-0.6481490910639609</v>
       </c>
       <c r="J4" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K4" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09047418063226231</v>
+        <v>0.09321165571255052</v>
       </c>
       <c r="M4" t="n">
-        <v>11.25556036862945</v>
+        <v>11.28359285207985</v>
       </c>
       <c r="N4" t="n">
-        <v>225.9878561084492</v>
+        <v>225.9731819845787</v>
       </c>
       <c r="O4" t="n">
-        <v>15.03289247312204</v>
+        <v>15.03240439798566</v>
       </c>
       <c r="P4" t="n">
-        <v>387.8986263032239</v>
+        <v>387.9946860365868</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33295,28 +33398,28 @@
         <v>0.1229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5489275422173174</v>
+        <v>-0.559985991115991</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04933925286936058</v>
+        <v>0.05142953616092749</v>
       </c>
       <c r="M5" t="n">
-        <v>14.19971893719083</v>
+        <v>14.22515831187624</v>
       </c>
       <c r="N5" t="n">
-        <v>319.8348719837492</v>
+        <v>319.8031057632542</v>
       </c>
       <c r="O5" t="n">
-        <v>17.88392775605373</v>
+        <v>17.88303961196905</v>
       </c>
       <c r="P5" t="n">
-        <v>397.9952915972567</v>
+        <v>398.1089336899628</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33373,28 +33476,28 @@
         <v>0.1248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.479721814616701</v>
+        <v>-0.4895770473111185</v>
       </c>
       <c r="J6" t="n">
+        <v>316</v>
+      </c>
+      <c r="K6" t="n">
         <v>315</v>
       </c>
-      <c r="K6" t="n">
-        <v>314</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03394992396965446</v>
+        <v>0.03546996822768778</v>
       </c>
       <c r="M6" t="n">
-        <v>14.93268676507166</v>
+        <v>14.94786920939051</v>
       </c>
       <c r="N6" t="n">
-        <v>360.3937154189574</v>
+        <v>360.0280801426468</v>
       </c>
       <c r="O6" t="n">
-        <v>18.98403843809207</v>
+        <v>18.97440592331277</v>
       </c>
       <c r="P6" t="n">
-        <v>391.6981908034544</v>
+        <v>391.7996602903738</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33451,28 +33554,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4058667316473417</v>
+        <v>-0.4113677389150273</v>
       </c>
       <c r="J7" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K7" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02523441020840256</v>
+        <v>0.02606163723283583</v>
       </c>
       <c r="M7" t="n">
-        <v>14.78862518222083</v>
+        <v>14.77686608440731</v>
       </c>
       <c r="N7" t="n">
-        <v>350.5393007988244</v>
+        <v>349.6725964096561</v>
       </c>
       <c r="O7" t="n">
-        <v>18.72269480600547</v>
+        <v>18.69953465756986</v>
       </c>
       <c r="P7" t="n">
-        <v>386.3000090605007</v>
+        <v>386.3565401331329</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33529,28 +33632,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1317617244622293</v>
+        <v>-0.131470140537845</v>
       </c>
       <c r="J8" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K8" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00236061752286465</v>
+        <v>0.002366373071023276</v>
       </c>
       <c r="M8" t="n">
-        <v>15.70355867592867</v>
+        <v>15.65485777676826</v>
       </c>
       <c r="N8" t="n">
-        <v>404.1934533378523</v>
+        <v>402.9150417293773</v>
       </c>
       <c r="O8" t="n">
-        <v>20.10456299793289</v>
+        <v>20.07274375189843</v>
       </c>
       <c r="P8" t="n">
-        <v>382.8321569247338</v>
+        <v>382.8291604640484</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33607,28 +33710,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07807045728044561</v>
+        <v>0.08137139308332267</v>
       </c>
       <c r="J9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007694107813950302</v>
+        <v>0.0008413852370040553</v>
       </c>
       <c r="M9" t="n">
-        <v>15.83422591933192</v>
+        <v>15.79591847803751</v>
       </c>
       <c r="N9" t="n">
-        <v>436.057414818808</v>
+        <v>434.7648388223361</v>
       </c>
       <c r="O9" t="n">
-        <v>20.88198780812804</v>
+        <v>20.8510152947605</v>
       </c>
       <c r="P9" t="n">
-        <v>382.4260793966244</v>
+        <v>382.3921573469803</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33685,28 +33788,28 @@
         <v>0.1309</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3620367429961585</v>
+        <v>0.3711826787703157</v>
       </c>
       <c r="J10" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K10" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01570052058728699</v>
+        <v>0.016578182722507</v>
       </c>
       <c r="M10" t="n">
-        <v>16.56300921795509</v>
+        <v>16.54736488276104</v>
       </c>
       <c r="N10" t="n">
-        <v>452.6695458600068</v>
+        <v>451.9076381626745</v>
       </c>
       <c r="O10" t="n">
-        <v>21.2760321925872</v>
+        <v>21.25811934679723</v>
       </c>
       <c r="P10" t="n">
-        <v>383.7937532600793</v>
+        <v>383.69976509857</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33763,28 +33866,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6563631420169027</v>
+        <v>0.6658353122891987</v>
       </c>
       <c r="J11" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K11" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05100132080591646</v>
+        <v>0.05266714373436887</v>
       </c>
       <c r="M11" t="n">
-        <v>16.70729157174841</v>
+        <v>16.692398820179</v>
       </c>
       <c r="N11" t="n">
-        <v>441.6063724553739</v>
+        <v>440.9281678217873</v>
       </c>
       <c r="O11" t="n">
-        <v>21.01443247997371</v>
+        <v>20.99828964039184</v>
       </c>
       <c r="P11" t="n">
-        <v>377.4024498179743</v>
+        <v>377.3051091093383</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33841,28 +33944,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8604591999357456</v>
+        <v>0.8730669288974866</v>
       </c>
       <c r="J12" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K12" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0742399453514434</v>
+        <v>0.07657227322293891</v>
       </c>
       <c r="M12" t="n">
-        <v>18.08321864842343</v>
+        <v>18.0783121721106</v>
       </c>
       <c r="N12" t="n">
-        <v>508.6091105727164</v>
+        <v>508.2738979985489</v>
       </c>
       <c r="O12" t="n">
-        <v>22.55236374690503</v>
+        <v>22.54493064967264</v>
       </c>
       <c r="P12" t="n">
-        <v>372.8317912162776</v>
+        <v>372.7022279550454</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33919,28 +34022,28 @@
         <v>0.1835</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7442564527191186</v>
+        <v>0.7585392201862924</v>
       </c>
       <c r="J13" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K13" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0519991585328663</v>
+        <v>0.05410620531547772</v>
       </c>
       <c r="M13" t="n">
-        <v>18.70471681594309</v>
+        <v>18.70820120269671</v>
       </c>
       <c r="N13" t="n">
-        <v>556.314527084722</v>
+        <v>556.1894458950001</v>
       </c>
       <c r="O13" t="n">
-        <v>23.58632076193152</v>
+        <v>23.58366905074357</v>
       </c>
       <c r="P13" t="n">
-        <v>379.2939698398397</v>
+        <v>379.147193054101</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33997,28 +34100,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7169887175807823</v>
+        <v>0.7350216628081673</v>
       </c>
       <c r="J14" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K14" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05251303910602967</v>
+        <v>0.05513258939678523</v>
       </c>
       <c r="M14" t="n">
-        <v>18.63413681658405</v>
+        <v>18.6454396063631</v>
       </c>
       <c r="N14" t="n">
-        <v>510.9677718659603</v>
+        <v>511.9577470369949</v>
       </c>
       <c r="O14" t="n">
-        <v>22.60459625531853</v>
+        <v>22.62648331131011</v>
       </c>
       <c r="P14" t="n">
-        <v>382.336087797583</v>
+        <v>382.1507723295575</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34075,28 +34178,28 @@
         <v>0.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2387565397719975</v>
+        <v>0.2656997467191466</v>
       </c>
       <c r="J15" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K15" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004001822013062983</v>
+        <v>0.004949720055302032</v>
       </c>
       <c r="M15" t="n">
-        <v>23.08320917827428</v>
+        <v>23.09926146934069</v>
       </c>
       <c r="N15" t="n">
-        <v>783.5746036517269</v>
+        <v>786.8017458529163</v>
       </c>
       <c r="O15" t="n">
-        <v>27.99240260591661</v>
+        <v>28.04998655708976</v>
       </c>
       <c r="P15" t="n">
-        <v>390.4383159843974</v>
+        <v>390.1626696698048</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34153,28 +34256,28 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2110149998067224</v>
+        <v>0.2427008841342675</v>
       </c>
       <c r="J16" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K16" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001153737499736796</v>
+        <v>0.001530554752197766</v>
       </c>
       <c r="M16" t="n">
-        <v>31.56768550193995</v>
+        <v>31.53329904398073</v>
       </c>
       <c r="N16" t="n">
-        <v>2066.433780564013</v>
+        <v>2067.575282258209</v>
       </c>
       <c r="O16" t="n">
-        <v>45.45804417882509</v>
+        <v>45.47059799758751</v>
       </c>
       <c r="P16" t="n">
-        <v>381.7949050706461</v>
+        <v>381.4625902630109</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34231,28 +34334,28 @@
         <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4801199465791256</v>
+        <v>0.5234433428949958</v>
       </c>
       <c r="J17" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K17" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L17" t="n">
-        <v>0.006721258263784446</v>
+        <v>0.007978006369436352</v>
       </c>
       <c r="M17" t="n">
-        <v>30.78363054381662</v>
+        <v>30.82487517354597</v>
       </c>
       <c r="N17" t="n">
-        <v>1809.543554180407</v>
+        <v>1817.125116115358</v>
       </c>
       <c r="O17" t="n">
-        <v>42.53873004898485</v>
+        <v>42.62775054017462</v>
       </c>
       <c r="P17" t="n">
-        <v>359.3333022670076</v>
+        <v>358.8796148277949</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34313,28 +34416,28 @@
         <v>0.0464</v>
       </c>
       <c r="I18" t="n">
-        <v>2.38158378064525</v>
+        <v>2.38242860667222</v>
       </c>
       <c r="J18" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K18" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2502815170123232</v>
+        <v>0.2517707025671558</v>
       </c>
       <c r="M18" t="n">
-        <v>23.49658906149294</v>
+        <v>23.4124569629234</v>
       </c>
       <c r="N18" t="n">
-        <v>956.0010740731371</v>
+        <v>952.5576541710445</v>
       </c>
       <c r="O18" t="n">
-        <v>30.91926703647965</v>
+        <v>30.86353275584382</v>
       </c>
       <c r="P18" t="n">
-        <v>329.6410339035341</v>
+        <v>329.6325050733415</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -34395,28 +34498,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>1.022346331266998</v>
+        <v>0.9784671582317447</v>
       </c>
       <c r="J19" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K19" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03140849931203327</v>
+        <v>0.02880609893425889</v>
       </c>
       <c r="M19" t="n">
-        <v>30.4541044946537</v>
+        <v>30.64233459844887</v>
       </c>
       <c r="N19" t="n">
-        <v>1798.111561318788</v>
+        <v>1807.475718821917</v>
       </c>
       <c r="O19" t="n">
-        <v>42.4041455676068</v>
+        <v>42.51441777587831</v>
       </c>
       <c r="P19" t="n">
-        <v>346.2763249566978</v>
+        <v>346.7242959928855</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -34477,28 +34580,28 @@
         <v>0.0269</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.21833285477959</v>
+        <v>-0.231285137073835</v>
       </c>
       <c r="J20" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K20" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001955963054894205</v>
+        <v>0.002207922444198762</v>
       </c>
       <c r="M20" t="n">
-        <v>24.59601623490624</v>
+        <v>24.59094719501183</v>
       </c>
       <c r="N20" t="n">
-        <v>1390.30888667765</v>
+        <v>1386.876078770081</v>
       </c>
       <c r="O20" t="n">
-        <v>37.28684602748871</v>
+        <v>37.24078515243846</v>
       </c>
       <c r="P20" t="n">
-        <v>362.704801242308</v>
+        <v>362.8357772868496</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -34559,28 +34662,28 @@
         <v>0.0312</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.964423266723055</v>
+        <v>-0.957377285596786</v>
       </c>
       <c r="J21" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K21" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02747251799410277</v>
+        <v>0.02726091875214287</v>
       </c>
       <c r="M21" t="n">
-        <v>30.05005359955236</v>
+        <v>29.98032054494851</v>
       </c>
       <c r="N21" t="n">
-        <v>1840.172730576932</v>
+        <v>1834.559315189885</v>
       </c>
       <c r="O21" t="n">
-        <v>42.89723453297347</v>
+        <v>42.83175591999335</v>
       </c>
       <c r="P21" t="n">
-        <v>359.3840342845893</v>
+        <v>359.3119568581457</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -34641,28 +34744,28 @@
         <v>0.0247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.690972645675528</v>
+        <v>0.6701403630308579</v>
       </c>
       <c r="J22" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K22" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03893730266138784</v>
+        <v>0.03689901076570845</v>
       </c>
       <c r="M22" t="n">
-        <v>19.26353132043547</v>
+        <v>19.25962663641917</v>
       </c>
       <c r="N22" t="n">
-        <v>652.405169715446</v>
+        <v>651.3908904165863</v>
       </c>
       <c r="O22" t="n">
-        <v>25.5422232727585</v>
+        <v>25.5223605964767</v>
       </c>
       <c r="P22" t="n">
-        <v>353.136012899546</v>
+        <v>353.3491488468633</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -34723,28 +34826,28 @@
         <v>0.0528</v>
       </c>
       <c r="I23" t="n">
-        <v>1.215943238727234</v>
+        <v>1.208727215457121</v>
       </c>
       <c r="J23" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K23" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1727054911357586</v>
+        <v>0.1718335516719411</v>
       </c>
       <c r="M23" t="n">
-        <v>15.07882176473464</v>
+        <v>15.07463451704685</v>
       </c>
       <c r="N23" t="n">
-        <v>391.3513372492301</v>
+        <v>390.5242965827952</v>
       </c>
       <c r="O23" t="n">
-        <v>19.78260188269556</v>
+        <v>19.76168759450455</v>
       </c>
       <c r="P23" t="n">
-        <v>336.6747174235467</v>
+        <v>336.7488626560909</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34801,28 +34904,28 @@
         <v>0.0794</v>
       </c>
       <c r="I24" t="n">
-        <v>1.160451357141703</v>
+        <v>1.154268996351474</v>
       </c>
       <c r="J24" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K24" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1384846588801651</v>
+        <v>0.1379500860312508</v>
       </c>
       <c r="M24" t="n">
-        <v>16.74984088104743</v>
+        <v>16.7241645137625</v>
       </c>
       <c r="N24" t="n">
-        <v>460.6277474514733</v>
+        <v>459.467091592571</v>
       </c>
       <c r="O24" t="n">
-        <v>21.4622400380639</v>
+        <v>21.43518349799159</v>
       </c>
       <c r="P24" t="n">
-        <v>335.6014968433881</v>
+        <v>335.6652687824086</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34879,28 +34982,28 @@
         <v>0.1141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.110164744599641</v>
+        <v>1.107402462442979</v>
       </c>
       <c r="J25" t="n">
+        <v>316</v>
+      </c>
+      <c r="K25" t="n">
         <v>315</v>
       </c>
-      <c r="K25" t="n">
-        <v>314</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1364198641160527</v>
+        <v>0.1366247485433459</v>
       </c>
       <c r="M25" t="n">
-        <v>16.02012785366533</v>
+        <v>15.9814111432215</v>
       </c>
       <c r="N25" t="n">
-        <v>430.6730436661201</v>
+        <v>429.367210154782</v>
       </c>
       <c r="O25" t="n">
-        <v>20.75266353184863</v>
+        <v>20.72117781774921</v>
       </c>
       <c r="P25" t="n">
-        <v>319.8247978680794</v>
+        <v>319.8531772094591</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34957,28 +35060,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9393522937259393</v>
+        <v>0.9400367053405061</v>
       </c>
       <c r="J26" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K26" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1160641285697491</v>
+        <v>0.1169204318521565</v>
       </c>
       <c r="M26" t="n">
-        <v>15.24107510282984</v>
+        <v>15.1960855323437</v>
       </c>
       <c r="N26" t="n">
-        <v>370.2052048842988</v>
+        <v>369.0374246518176</v>
       </c>
       <c r="O26" t="n">
-        <v>19.24071736927443</v>
+        <v>19.21034681237737</v>
       </c>
       <c r="P26" t="n">
-        <v>300.8630803220225</v>
+        <v>300.856046969618</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35035,28 +35138,28 @@
         <v>0.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8706780774212752</v>
+        <v>0.8739800047744657</v>
       </c>
       <c r="J27" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K27" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1180784396344458</v>
+        <v>0.1195612908193527</v>
       </c>
       <c r="M27" t="n">
-        <v>13.96761213834211</v>
+        <v>13.93937205324086</v>
       </c>
       <c r="N27" t="n">
-        <v>311.9157826165528</v>
+        <v>311.0161123731378</v>
       </c>
       <c r="O27" t="n">
-        <v>17.66113763653273</v>
+        <v>17.63564890706146</v>
       </c>
       <c r="P27" t="n">
-        <v>287.8844561858941</v>
+        <v>287.8505239465883</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35113,28 +35216,28 @@
         <v>0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8948240124683876</v>
+        <v>0.8973957453508182</v>
       </c>
       <c r="J28" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K28" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1432943062322382</v>
+        <v>0.1448247210416759</v>
       </c>
       <c r="M28" t="n">
-        <v>12.97798368062196</v>
+        <v>12.9505414327324</v>
       </c>
       <c r="N28" t="n">
-        <v>263.7185961637164</v>
+        <v>262.9370652717316</v>
       </c>
       <c r="O28" t="n">
-        <v>16.23941489597813</v>
+        <v>16.21533426333641</v>
       </c>
       <c r="P28" t="n">
-        <v>278.2934043150889</v>
+        <v>278.2669759154717</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35172,7 +35275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC316"/>
+  <dimension ref="A1:AC317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81180,7 +81283,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>-43.21951180504154,170.1609822303193</t>
+          <t>-43.21944464511276,170.16091190988672</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
@@ -81200,7 +81303,7 @@
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>-43.21793578489049,170.16386978172483</t>
+          <t>-43.21802293039694,170.16395487630385</t>
         </is>
       </c>
       <c r="W316" t="inlineStr">
@@ -81234,6 +81337,153 @@
         </is>
       </c>
       <c r="AC316" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-43.22612418221276,170.15019085222505</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-43.22599948037879,170.151081822051</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-43.22572418428392,170.15190147153723</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-43.225422772848695,170.15267106466283</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-43.22506632384306,170.15336969720934</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-43.22463074855452,170.15403716636055</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-43.2241256432916,170.15463640930048</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-43.22364243485329,170.15525888409647</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-43.2231191055458,170.1557875080221</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-43.22267183351282,170.15636201129806</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-43.22216150771778,170.1569063860272</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-43.22164118279296,170.1574595441666</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>-43.2211069632811,170.1579928997851</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-43.2205668227077,170.15851781975906</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>-43.22009974678921,170.1591469043833</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>-43.21958598301478,170.15980531365508</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>-43.219486298562614,170.1609555234987</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>-43.219670234013726,170.1622567568168</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>-43.219039798047845,170.1627433745371</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>-43.21858826611175,170.16340468743508</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>-43.218157456582254,170.1640862370611</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>-43.21771675861353,170.1647581329071</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>-43.217336727730974,170.1654718442402</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>-43.216922324837334,170.16614528559288</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>-43.216471420430715,170.1668270587931</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>-43.21598319099444,170.1674350048056</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>-43.21549246611196,170.168038123903</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0425/nzd0425.xlsx
+++ b/data/nzd0425/nzd0425.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC317"/>
+  <dimension ref="A1:AC318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29647,13 +29647,13 @@
         <v>321.91</v>
       </c>
       <c r="T316" t="n">
-        <v>354.99</v>
+        <v>376.68</v>
       </c>
       <c r="U316" t="n">
-        <v>369.91</v>
+        <v>389.32</v>
       </c>
       <c r="V316" t="n">
-        <v>368.82</v>
+        <v>380.72</v>
       </c>
       <c r="W316" t="n">
         <v>364.57</v>
@@ -29740,13 +29740,13 @@
         <v>304.55</v>
       </c>
       <c r="T317" t="n">
-        <v>337.08</v>
+        <v>376.68</v>
       </c>
       <c r="U317" t="n">
-        <v>345.18</v>
+        <v>369.3</v>
       </c>
       <c r="V317" t="n">
-        <v>350.45</v>
+        <v>379.32</v>
       </c>
       <c r="W317" t="n">
         <v>357.07</v>
@@ -29767,6 +29767,99 @@
         <v>305.91</v>
       </c>
       <c r="AC317" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:29+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="C318" t="n">
+        <v>353.02</v>
+      </c>
+      <c r="D318" t="n">
+        <v>357.08</v>
+      </c>
+      <c r="E318" t="n">
+        <v>365.76</v>
+      </c>
+      <c r="F318" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="G318" t="n">
+        <v>367.33</v>
+      </c>
+      <c r="H318" t="n">
+        <v>380.58</v>
+      </c>
+      <c r="I318" t="n">
+        <v>393.72</v>
+      </c>
+      <c r="J318" t="n">
+        <v>412.33</v>
+      </c>
+      <c r="K318" t="n">
+        <v>415.63</v>
+      </c>
+      <c r="L318" t="n">
+        <v>417.55</v>
+      </c>
+      <c r="M318" t="n">
+        <v>425.27</v>
+      </c>
+      <c r="N318" t="n">
+        <v>435.58</v>
+      </c>
+      <c r="O318" t="n">
+        <v>445.59</v>
+      </c>
+      <c r="P318" t="n">
+        <v>443.09</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>444.89</v>
+      </c>
+      <c r="R318" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="S318" t="n">
+        <v>300.49</v>
+      </c>
+      <c r="T318" t="n">
+        <v>415.81</v>
+      </c>
+      <c r="U318" t="n">
+        <v>392.31</v>
+      </c>
+      <c r="V318" t="n">
+        <v>367.25</v>
+      </c>
+      <c r="W318" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="X318" t="n">
+        <v>356.51</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>343.46</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>326.1</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>317.31</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>307.25</v>
+      </c>
+      <c r="AC318" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29783,7 +29876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B321"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32996,6 +33089,16 @@
       </c>
       <c r="B321" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>
@@ -33164,28 +33267,28 @@
         <v>0.1361</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7615334912785322</v>
+        <v>-0.765058286118645</v>
       </c>
       <c r="J2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2086791423864535</v>
+        <v>0.2112383647177463</v>
       </c>
       <c r="M2" t="n">
-        <v>8.484401624457048</v>
+        <v>8.474550436100548</v>
       </c>
       <c r="N2" t="n">
-        <v>121.5970242886782</v>
+        <v>121.3115780047257</v>
       </c>
       <c r="O2" t="n">
-        <v>11.02710407535352</v>
+        <v>11.01415353101298</v>
       </c>
       <c r="P2" t="n">
-        <v>388.2418512674314</v>
+        <v>388.2783555225473</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33242,28 +33345,28 @@
         <v>0.1113</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7948086146639979</v>
+        <v>-0.8022313221034841</v>
       </c>
       <c r="J3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1421701834525344</v>
+        <v>0.1450633614858644</v>
       </c>
       <c r="M3" t="n">
-        <v>10.96904544143041</v>
+        <v>10.97088152794117</v>
       </c>
       <c r="N3" t="n">
-        <v>210.7604448297509</v>
+        <v>210.5308019879755</v>
       </c>
       <c r="O3" t="n">
-        <v>14.5175908755465</v>
+        <v>14.50967959632381</v>
       </c>
       <c r="P3" t="n">
-        <v>385.8343980291282</v>
+        <v>385.9112707035142</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33320,28 +33423,28 @@
         <v>0.1963</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6481490910639609</v>
+        <v>-0.6568109341641151</v>
       </c>
       <c r="J4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09321165571255052</v>
+        <v>0.09585868116500296</v>
       </c>
       <c r="M4" t="n">
-        <v>11.28359285207985</v>
+        <v>11.3064863976705</v>
       </c>
       <c r="N4" t="n">
-        <v>225.9731819845787</v>
+        <v>225.8529870701297</v>
       </c>
       <c r="O4" t="n">
-        <v>15.03240439798566</v>
+        <v>15.02840600563246</v>
       </c>
       <c r="P4" t="n">
-        <v>387.9946860365868</v>
+        <v>388.0843917200789</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33398,28 +33501,28 @@
         <v>0.1229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.559985991115991</v>
+        <v>-0.5710181888962134</v>
       </c>
       <c r="J5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05142953616092749</v>
+        <v>0.0535686823171847</v>
       </c>
       <c r="M5" t="n">
-        <v>14.22515831187624</v>
+        <v>14.2493416178674</v>
       </c>
       <c r="N5" t="n">
-        <v>319.8031057632542</v>
+        <v>319.7556647761453</v>
       </c>
       <c r="O5" t="n">
-        <v>17.88303961196905</v>
+        <v>17.88171313873884</v>
       </c>
       <c r="P5" t="n">
-        <v>398.1089336899628</v>
+        <v>398.2231877616252</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33476,28 +33579,28 @@
         <v>0.1248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4895770473111185</v>
+        <v>-0.4982729894014674</v>
       </c>
       <c r="J6" t="n">
+        <v>317</v>
+      </c>
+      <c r="K6" t="n">
         <v>316</v>
       </c>
-      <c r="K6" t="n">
-        <v>315</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03546996822768778</v>
+        <v>0.03688359621498449</v>
       </c>
       <c r="M6" t="n">
-        <v>14.94786920939051</v>
+        <v>14.95693271989779</v>
       </c>
       <c r="N6" t="n">
-        <v>360.0280801426468</v>
+        <v>359.4859066144924</v>
       </c>
       <c r="O6" t="n">
-        <v>18.97440592331277</v>
+        <v>18.96011357071714</v>
       </c>
       <c r="P6" t="n">
-        <v>391.7996602903738</v>
+        <v>391.8898914712651</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33554,28 +33657,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4113677389150273</v>
+        <v>-0.4164928392943164</v>
       </c>
       <c r="J7" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K7" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02606163723283583</v>
+        <v>0.02686462051711802</v>
       </c>
       <c r="M7" t="n">
-        <v>14.77686608440731</v>
+        <v>14.76271970541921</v>
       </c>
       <c r="N7" t="n">
-        <v>349.6725964096561</v>
+        <v>348.7770127169951</v>
       </c>
       <c r="O7" t="n">
-        <v>18.69953465756986</v>
+        <v>18.67557262085945</v>
       </c>
       <c r="P7" t="n">
-        <v>386.3565401331329</v>
+        <v>386.4096178242402</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33632,28 +33735,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.131470140537845</v>
+        <v>-0.1307010987081659</v>
       </c>
       <c r="J8" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K8" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002366373071023276</v>
+        <v>0.002355202695276115</v>
       </c>
       <c r="M8" t="n">
-        <v>15.65485777676826</v>
+        <v>15.60803607692525</v>
       </c>
       <c r="N8" t="n">
-        <v>402.9150417293773</v>
+        <v>401.6486881229928</v>
       </c>
       <c r="O8" t="n">
-        <v>20.07274375189843</v>
+        <v>20.04117481893197</v>
       </c>
       <c r="P8" t="n">
-        <v>382.8291604640484</v>
+        <v>382.8211959440072</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33710,28 +33813,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08137139308332267</v>
+        <v>0.08714010404689129</v>
       </c>
       <c r="J9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008413852370040553</v>
+        <v>0.0009709769223656961</v>
       </c>
       <c r="M9" t="n">
-        <v>15.79591847803751</v>
+        <v>15.76626032017078</v>
       </c>
       <c r="N9" t="n">
-        <v>434.7648388223361</v>
+        <v>433.6562092764889</v>
       </c>
       <c r="O9" t="n">
-        <v>20.8510152947605</v>
+        <v>20.8244137799</v>
       </c>
       <c r="P9" t="n">
-        <v>382.3921573469803</v>
+        <v>382.3324141544667</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33788,28 +33891,28 @@
         <v>0.1309</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3711826787703157</v>
+        <v>0.3830118937716538</v>
       </c>
       <c r="J10" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K10" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L10" t="n">
-        <v>0.016578182722507</v>
+        <v>0.01771176643247618</v>
       </c>
       <c r="M10" t="n">
-        <v>16.54736488276104</v>
+        <v>16.54573337391897</v>
       </c>
       <c r="N10" t="n">
-        <v>451.9076381626745</v>
+        <v>451.5873937063334</v>
       </c>
       <c r="O10" t="n">
-        <v>21.25811934679723</v>
+        <v>21.25058572619431</v>
       </c>
       <c r="P10" t="n">
-        <v>383.69976509857</v>
+        <v>383.5772567819682</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33866,28 +33969,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6658353122891987</v>
+        <v>0.6788654373658167</v>
       </c>
       <c r="J11" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K11" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05266714373436887</v>
+        <v>0.05483960691724865</v>
       </c>
       <c r="M11" t="n">
-        <v>16.692398820179</v>
+        <v>16.69137755312211</v>
       </c>
       <c r="N11" t="n">
-        <v>440.9281678217873</v>
+        <v>440.8783790377346</v>
       </c>
       <c r="O11" t="n">
-        <v>20.99828964039184</v>
+        <v>20.99710406312581</v>
       </c>
       <c r="P11" t="n">
-        <v>377.3051091093383</v>
+        <v>377.1701636638404</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33944,28 +34047,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8730669288974866</v>
+        <v>0.8867526427697029</v>
       </c>
       <c r="J12" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K12" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07657227322293891</v>
+        <v>0.07909819782162741</v>
       </c>
       <c r="M12" t="n">
-        <v>18.0783121721106</v>
+        <v>18.07701888233137</v>
       </c>
       <c r="N12" t="n">
-        <v>508.2738979985489</v>
+        <v>508.1500127361812</v>
       </c>
       <c r="O12" t="n">
-        <v>22.54493064967264</v>
+        <v>22.54218296297369</v>
       </c>
       <c r="P12" t="n">
-        <v>372.7022279550454</v>
+        <v>372.560492956756</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34022,28 +34125,28 @@
         <v>0.1835</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7585392201862924</v>
+        <v>0.7749334144149482</v>
       </c>
       <c r="J13" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K13" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05410620531547772</v>
+        <v>0.05650639027325421</v>
       </c>
       <c r="M13" t="n">
-        <v>18.70820120269671</v>
+        <v>18.71975903722932</v>
       </c>
       <c r="N13" t="n">
-        <v>556.1894458950001</v>
+        <v>556.557958479106</v>
       </c>
       <c r="O13" t="n">
-        <v>23.58366905074357</v>
+        <v>23.59148063346398</v>
       </c>
       <c r="P13" t="n">
-        <v>379.147193054101</v>
+        <v>378.9774078961873</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34100,28 +34203,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7350216628081673</v>
+        <v>0.7563974826818306</v>
       </c>
       <c r="J14" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K14" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05513258939678523</v>
+        <v>0.05819412620794417</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6454396063631</v>
+        <v>18.66979630011054</v>
       </c>
       <c r="N14" t="n">
-        <v>511.9577470369949</v>
+        <v>513.9520662230209</v>
       </c>
       <c r="O14" t="n">
-        <v>22.62648331131011</v>
+        <v>22.67051093872877</v>
       </c>
       <c r="P14" t="n">
-        <v>382.1507723295575</v>
+        <v>381.9293953651173</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34178,28 +34281,28 @@
         <v>0.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2656997467191466</v>
+        <v>0.296502198160094</v>
       </c>
       <c r="J15" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K15" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004949720055302032</v>
+        <v>0.006142697673878872</v>
       </c>
       <c r="M15" t="n">
-        <v>23.09926146934069</v>
+        <v>23.12602713022644</v>
       </c>
       <c r="N15" t="n">
-        <v>786.8017458529163</v>
+        <v>791.6792418543463</v>
       </c>
       <c r="O15" t="n">
-        <v>28.04998655708976</v>
+        <v>28.13679515961877</v>
       </c>
       <c r="P15" t="n">
-        <v>390.1626696698048</v>
+        <v>389.8450992479596</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34256,28 +34359,28 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2427008841342675</v>
+        <v>0.2782649040226067</v>
       </c>
       <c r="J16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K16" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001530554752197766</v>
+        <v>0.002015896413553819</v>
       </c>
       <c r="M16" t="n">
-        <v>31.53329904398073</v>
+        <v>31.50528954159487</v>
       </c>
       <c r="N16" t="n">
-        <v>2067.575282258209</v>
+        <v>2070.600467726993</v>
       </c>
       <c r="O16" t="n">
-        <v>45.47059799758751</v>
+        <v>45.50385113072291</v>
       </c>
       <c r="P16" t="n">
-        <v>381.4625902630109</v>
+        <v>381.086765521202</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34334,28 +34437,28 @@
         <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5234433428949958</v>
+        <v>0.5721792291548021</v>
       </c>
       <c r="J17" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K17" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L17" t="n">
-        <v>0.007978006369436352</v>
+        <v>0.009501194537716806</v>
       </c>
       <c r="M17" t="n">
-        <v>30.82487517354597</v>
+        <v>30.88352087226086</v>
       </c>
       <c r="N17" t="n">
-        <v>1817.125116115358</v>
+        <v>1828.060386249223</v>
       </c>
       <c r="O17" t="n">
-        <v>42.62775054017462</v>
+        <v>42.75582283443067</v>
       </c>
       <c r="P17" t="n">
-        <v>358.8796148277949</v>
+        <v>358.3654694764211</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34416,28 +34519,28 @@
         <v>0.0464</v>
       </c>
       <c r="I18" t="n">
-        <v>2.38242860667222</v>
+        <v>2.385801890885276</v>
       </c>
       <c r="J18" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K18" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2517707025671558</v>
+        <v>0.2536311777051158</v>
       </c>
       <c r="M18" t="n">
-        <v>23.4124569629234</v>
+        <v>23.3502966636797</v>
       </c>
       <c r="N18" t="n">
-        <v>952.5576541710445</v>
+        <v>949.4406902204105</v>
       </c>
       <c r="O18" t="n">
-        <v>30.86353275584382</v>
+        <v>30.81299547626635</v>
       </c>
       <c r="P18" t="n">
-        <v>329.6325050733415</v>
+        <v>329.5976518148578</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -34498,28 +34601,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9784671582317447</v>
+        <v>0.9320751026111869</v>
       </c>
       <c r="J19" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K19" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02880609893425889</v>
+        <v>0.02615511074465571</v>
       </c>
       <c r="M19" t="n">
-        <v>30.64233459844887</v>
+        <v>30.84151219664748</v>
       </c>
       <c r="N19" t="n">
-        <v>1807.475718821917</v>
+        <v>1818.383858901125</v>
       </c>
       <c r="O19" t="n">
-        <v>42.51441777587831</v>
+        <v>42.6425123427446</v>
       </c>
       <c r="P19" t="n">
-        <v>346.7242959928855</v>
+        <v>347.2016727980914</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -34580,28 +34683,28 @@
         <v>0.0269</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.231285137073835</v>
+        <v>-0.1531605450766317</v>
       </c>
       <c r="J20" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K20" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002207922444198762</v>
+        <v>0.0009675333086874849</v>
       </c>
       <c r="M20" t="n">
-        <v>24.59094719501183</v>
+        <v>24.68791213143895</v>
       </c>
       <c r="N20" t="n">
-        <v>1386.876078770081</v>
+        <v>1394.942966401956</v>
       </c>
       <c r="O20" t="n">
-        <v>37.24078515243846</v>
+        <v>37.34893527802307</v>
       </c>
       <c r="P20" t="n">
-        <v>362.8357772868496</v>
+        <v>362.0428641401106</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -34662,28 +34765,28 @@
         <v>0.0312</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.957377285596786</v>
+        <v>-0.8929883712610305</v>
       </c>
       <c r="J21" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K21" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02726091875214287</v>
+        <v>0.02371195058944686</v>
       </c>
       <c r="M21" t="n">
-        <v>29.98032054494851</v>
+        <v>30.14009652528887</v>
       </c>
       <c r="N21" t="n">
-        <v>1834.559315189885</v>
+        <v>1848.683013905758</v>
       </c>
       <c r="O21" t="n">
-        <v>42.83175591999335</v>
+        <v>42.99631395719589</v>
       </c>
       <c r="P21" t="n">
-        <v>359.3119568581457</v>
+        <v>358.6505247957959</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -34744,28 +34847,28 @@
         <v>0.0247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6701403630308579</v>
+        <v>0.6933845951595676</v>
       </c>
       <c r="J22" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K22" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03689901076570845</v>
+        <v>0.03972096026987948</v>
       </c>
       <c r="M22" t="n">
-        <v>19.25962663641917</v>
+        <v>19.17696235582643</v>
       </c>
       <c r="N22" t="n">
-        <v>651.3908904165863</v>
+        <v>648.4595453761974</v>
       </c>
       <c r="O22" t="n">
-        <v>25.5223605964767</v>
+        <v>25.46486884663256</v>
       </c>
       <c r="P22" t="n">
-        <v>353.3491488468633</v>
+        <v>353.1115352211373</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -34826,28 +34929,28 @@
         <v>0.0528</v>
       </c>
       <c r="I23" t="n">
-        <v>1.208727215457121</v>
+        <v>1.197652455554666</v>
       </c>
       <c r="J23" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K23" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1718335516719411</v>
+        <v>0.1698626653077376</v>
       </c>
       <c r="M23" t="n">
-        <v>15.07463451704685</v>
+        <v>15.09407007691573</v>
       </c>
       <c r="N23" t="n">
-        <v>390.5242965827952</v>
+        <v>390.2576110879125</v>
       </c>
       <c r="O23" t="n">
-        <v>19.76168759450455</v>
+        <v>19.75493890367451</v>
       </c>
       <c r="P23" t="n">
-        <v>336.7488626560909</v>
+        <v>336.8635487581577</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34904,28 +35007,28 @@
         <v>0.0794</v>
       </c>
       <c r="I24" t="n">
-        <v>1.154268996351474</v>
+        <v>1.148164941859609</v>
       </c>
       <c r="J24" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K24" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1379500860312508</v>
+        <v>0.1374449038356337</v>
       </c>
       <c r="M24" t="n">
-        <v>16.7241645137625</v>
+        <v>16.69784290571835</v>
       </c>
       <c r="N24" t="n">
-        <v>459.467091592571</v>
+        <v>458.30263861419</v>
       </c>
       <c r="O24" t="n">
-        <v>21.43518349799159</v>
+        <v>21.40800407824583</v>
       </c>
       <c r="P24" t="n">
-        <v>335.6652687824086</v>
+        <v>335.7287247067745</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34982,28 +35085,28 @@
         <v>0.1141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.107402462442979</v>
+        <v>1.10383634000211</v>
       </c>
       <c r="J25" t="n">
+        <v>317</v>
+      </c>
+      <c r="K25" t="n">
         <v>316</v>
       </c>
-      <c r="K25" t="n">
-        <v>315</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1366247485433459</v>
+        <v>0.1366608424529365</v>
       </c>
       <c r="M25" t="n">
-        <v>15.9814111432215</v>
+        <v>15.94639889455561</v>
       </c>
       <c r="N25" t="n">
-        <v>429.367210154782</v>
+        <v>428.1092526460134</v>
       </c>
       <c r="O25" t="n">
-        <v>20.72117781774921</v>
+        <v>20.6908011600811</v>
       </c>
       <c r="P25" t="n">
-        <v>319.8531772094591</v>
+        <v>319.89010144233</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35060,28 +35163,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9400367053405061</v>
+        <v>0.9402855808199593</v>
       </c>
       <c r="J26" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K26" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1169204318521565</v>
+        <v>0.1177001874025041</v>
       </c>
       <c r="M26" t="n">
-        <v>15.1960855323437</v>
+        <v>15.14930472199548</v>
       </c>
       <c r="N26" t="n">
-        <v>369.0374246518176</v>
+        <v>367.8737580040364</v>
       </c>
       <c r="O26" t="n">
-        <v>19.21034681237737</v>
+        <v>19.18003540153241</v>
       </c>
       <c r="P26" t="n">
-        <v>300.856046969618</v>
+        <v>300.8534695106718</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35138,28 +35241,28 @@
         <v>0.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8739800047744657</v>
+        <v>0.8779783972485798</v>
       </c>
       <c r="J27" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K27" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1195612908193527</v>
+        <v>0.1212264258197652</v>
       </c>
       <c r="M27" t="n">
-        <v>13.93937205324086</v>
+        <v>13.91436776710507</v>
       </c>
       <c r="N27" t="n">
-        <v>311.0161123731378</v>
+        <v>310.1612739450636</v>
       </c>
       <c r="O27" t="n">
-        <v>17.63564890706146</v>
+        <v>17.61139613844012</v>
       </c>
       <c r="P27" t="n">
-        <v>287.8505239465883</v>
+        <v>287.8091149155528</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35216,28 +35319,28 @@
         <v>0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8973957453508182</v>
+        <v>0.900700118446592</v>
       </c>
       <c r="J28" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K28" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1448247210416759</v>
+        <v>0.1465702771276635</v>
       </c>
       <c r="M28" t="n">
-        <v>12.9505414327324</v>
+        <v>12.92688398266928</v>
       </c>
       <c r="N28" t="n">
-        <v>262.9370652717316</v>
+        <v>262.1938607717376</v>
       </c>
       <c r="O28" t="n">
-        <v>16.21533426333641</v>
+        <v>16.19240132814579</v>
       </c>
       <c r="P28" t="n">
-        <v>278.2669759154717</v>
+        <v>278.232754440476</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35275,7 +35378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC317"/>
+  <dimension ref="A1:AC318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81293,17 +81396,17 @@
       </c>
       <c r="T316" t="inlineStr">
         <is>
-          <t>-43.21890863958468,170.1626153033483</t>
+          <t>-43.218749799260785,170.16246020278572</t>
         </is>
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>-43.218407164034225,170.1632278477212</t>
+          <t>-43.218265021064454,170.16308905108025</t>
         </is>
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>-43.21802293039694,170.16395487630385</t>
+          <t>-43.21793578489049,170.16386978172483</t>
         </is>
       </c>
       <c r="W316" t="inlineStr">
@@ -81440,17 +81543,17 @@
       </c>
       <c r="T317" t="inlineStr">
         <is>
-          <t>-43.219039798047845,170.1627433745371</t>
+          <t>-43.218749799260785,170.16246020278572</t>
         </is>
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>-43.21858826611175,170.16340468743508</t>
+          <t>-43.218411631173,170.16323220970736</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>-43.218157456582254,170.1640862370611</t>
+          <t>-43.21794603730601,170.16387979283937</t>
         </is>
       </c>
       <c r="W317" t="inlineStr">
@@ -81484,6 +81587,153 @@
         </is>
       </c>
       <c r="AC317" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:29+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-43.22612656313937,170.15019197980556</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-43.22597907247974,170.15107215688718</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-43.22571644630356,170.15189780677304</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-43.22542381260881,170.15267179781281</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-43.2250541230802,170.15335728220714</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-43.224627264610724,170.15403347038315</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-43.22412038184287,170.15463082763097</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-43.22361427908869,170.15522901466812</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-43.22308914859126,170.15575210425308</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-43.222634695082625,170.15631116666094</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-43.222149360660865,170.15688906947526</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-43.221618882138586,170.15742775288268</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>-43.22107226659401,170.1579434370355</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-43.220527516565355,170.1584617859161</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>-43.22006069002066,170.1590912258669</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>-43.219530111026565,170.15973460527857</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>-43.219388559397196,170.16085318496184</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>-43.219699966238714,170.16228578937753</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>-43.218463241750726,170.1621803945162</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>-43.21824312473553,170.16306767030449</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>-43.21803442774098,170.1639661030855</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>-43.21776040437764,170.16480075201264</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>-43.21733478193584,170.16546946644746</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>-43.216928489220614,170.1661558753229</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>-43.21647416970327,170.16683238745082</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>-43.215976551291085,170.16742213564498</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>-43.2154855152245,170.1680246515524</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
